--- a/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
@@ -91,6 +91,9 @@
     <t>CUCHILLA ARTE AK-1/5B</t>
   </si>
   <si>
+    <t>⚠ BAJO</t>
+  </si>
+  <si>
     <t>85164</t>
   </si>
   <si>
@@ -233,9 +236,6 @@
   </si>
   <si>
     <t>CUCHILLA HEAVY DUTY L-5 AL</t>
-  </si>
-  <si>
-    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>85823</t>
@@ -1591,12 +1591,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -1619,12 +1619,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -2167,11 +2167,11 @@
       <c r="E7">
         <v>120</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>1031</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="G7" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2179,22 +2179,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>268</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2202,22 +2202,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>253</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2225,22 +2225,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>59</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2248,22 +2248,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>37</v>
+      <c r="G11" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2271,22 +2271,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>132</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2294,22 +2294,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>191</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2317,22 +2317,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>189</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2340,22 +2340,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>84</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2363,22 +2363,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16">
         <v>120</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>692</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="G16" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2386,22 +2386,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="4">
         <v>257</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="G17" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2409,22 +2409,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>120</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="4">
         <v>983</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+      <c r="G18" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2432,22 +2432,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>195</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="G19" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2455,22 +2455,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="4">
         <v>75</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2478,22 +2478,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="4">
         <v>439</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="G21" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2501,13 +2501,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E22">
         <v>120</v>
@@ -2524,22 +2524,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="4">
         <v>3</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>74</v>
+      <c r="G23" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2558,11 +2558,11 @@
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="4">
         <v>113</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="G24" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2581,11 +2581,11 @@
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="4">
         <v>348</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="G25" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2604,11 +2604,11 @@
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="4">
         <v>123</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="G26" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2627,11 +2627,11 @@
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="4">
         <v>160</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="G27" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2673,11 +2673,11 @@
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="4">
         <v>94</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="G29" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2696,11 +2696,11 @@
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="4">
         <v>56</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="G30" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2765,11 +2765,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="6">
         <v>0</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>37</v>
+      <c r="G33" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2788,11 +2788,11 @@
       <c r="E34">
         <v>120</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="4">
         <v>907</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>10</v>
+      <c r="G34" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2811,11 +2811,11 @@
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="6">
         <v>0</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>37</v>
+      <c r="G35" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2834,11 +2834,11 @@
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="4">
         <v>118</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="G36" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2857,11 +2857,11 @@
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="4">
         <v>944</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="G37" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2880,11 +2880,11 @@
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="4">
         <v>123</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="G38" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2903,11 +2903,11 @@
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="4">
         <v>278</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="G39" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2926,11 +2926,11 @@
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="4">
         <v>245</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="G40" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2949,11 +2949,11 @@
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="4">
         <v>107</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="G41" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2972,11 +2972,11 @@
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="4">
         <v>273</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="G42" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3018,11 +3018,11 @@
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="4">
         <v>1090</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="G44" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3041,11 +3041,11 @@
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="4">
         <v>163</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="G45" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3064,11 +3064,11 @@
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="4">
         <v>1475</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>10</v>
+      <c r="G46" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3087,11 +3087,11 @@
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="4">
         <v>164</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="G47" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3110,11 +3110,11 @@
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="4">
         <v>140</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="G48" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3133,11 +3133,11 @@
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="4">
         <v>261</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+      <c r="G49" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3156,11 +3156,11 @@
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="4">
         <v>291</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="G50" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3179,11 +3179,11 @@
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="4">
         <v>10</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>10</v>
+      <c r="G51" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3202,11 +3202,11 @@
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="4">
         <v>82</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="G52" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3225,11 +3225,11 @@
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="4">
         <v>27</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="G53" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3248,11 +3248,11 @@
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="4">
         <v>2462</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="G54" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3271,11 +3271,11 @@
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="4">
         <v>208</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="G55" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3294,11 +3294,11 @@
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="6">
         <v>0</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>37</v>
+      <c r="G56" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3317,11 +3317,11 @@
       <c r="E57">
         <v>720</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="4">
         <v>4873</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="G57" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3340,11 +3340,11 @@
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="4">
         <v>201</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="G58" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3363,11 +3363,11 @@
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="6">
         <v>0</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>37</v>
+      <c r="G59" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3386,11 +3386,11 @@
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="6">
         <v>0</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>37</v>
+      <c r="G60" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3409,11 +3409,11 @@
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="4">
         <v>300</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>10</v>
+      <c r="G61" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3432,11 +3432,11 @@
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="4">
         <v>198</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="G62" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3478,11 +3478,11 @@
       <c r="E64">
         <v>60</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="4">
         <v>513</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>10</v>
+      <c r="G64" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3501,11 +3501,11 @@
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="4">
         <v>65</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="G65" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3524,11 +3524,11 @@
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="4">
         <v>69</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="G66" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3547,11 +3547,11 @@
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="6">
         <v>0</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>37</v>
+      <c r="G67" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3570,11 +3570,11 @@
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="4">
         <v>55</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="G68" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3616,11 +3616,11 @@
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="4">
         <v>130</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="G70" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3639,11 +3639,11 @@
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="4">
+      <c r="F71" s="6">
         <v>0</v>
       </c>
-      <c r="G71" s="5" t="s">
-        <v>37</v>
+      <c r="G71" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3662,11 +3662,11 @@
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="4">
         <v>412</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+      <c r="G72" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3685,11 +3685,11 @@
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="4">
         <v>500</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="G73" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3708,11 +3708,11 @@
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="4">
         <v>1529</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="G74" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3754,11 +3754,11 @@
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F76" s="6">
         <v>0</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>37</v>
+      <c r="G76" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3777,11 +3777,11 @@
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="4">
         <v>539</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="G77" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3800,11 +3800,11 @@
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="4">
         <v>114</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="G78" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3823,11 +3823,11 @@
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="4">
         <v>4</v>
       </c>
-      <c r="G79" s="7" t="s">
-        <v>74</v>
+      <c r="G79" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3846,11 +3846,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="4">
         <v>12</v>
       </c>
-      <c r="G80" s="3" t="s">
-        <v>10</v>
+      <c r="G80" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3915,11 +3915,11 @@
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="6">
         <v>0</v>
       </c>
-      <c r="G83" s="5" t="s">
-        <v>37</v>
+      <c r="G83" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3938,11 +3938,11 @@
       <c r="E84">
         <v>40</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="4">
         <v>80</v>
       </c>
-      <c r="G84" s="3" t="s">
-        <v>10</v>
+      <c r="G84" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3961,11 +3961,11 @@
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="4">
+      <c r="F85" s="6">
         <v>0</v>
       </c>
-      <c r="G85" s="5" t="s">
-        <v>37</v>
+      <c r="G85" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3984,11 +3984,11 @@
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="6">
         <v>0</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>37</v>
+      <c r="G86" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4007,11 +4007,11 @@
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="4">
+      <c r="F87" s="6">
         <v>0</v>
       </c>
-      <c r="G87" s="5" t="s">
-        <v>37</v>
+      <c r="G87" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4030,11 +4030,11 @@
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="6">
         <v>0</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>37</v>
+      <c r="G88" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4099,11 +4099,11 @@
       <c r="E91">
         <v>10</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="4">
         <v>68</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>10</v>
+      <c r="G91" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4191,11 +4191,11 @@
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="4">
+      <c r="F95" s="6">
         <v>0</v>
       </c>
-      <c r="G95" s="5" t="s">
-        <v>37</v>
+      <c r="G95" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4214,11 +4214,11 @@
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="4">
+      <c r="F96" s="6">
         <v>0</v>
       </c>
-      <c r="G96" s="5" t="s">
-        <v>37</v>
+      <c r="G96" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4237,11 +4237,11 @@
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="4">
         <v>7</v>
       </c>
-      <c r="G97" s="7" t="s">
-        <v>74</v>
+      <c r="G97" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4260,11 +4260,11 @@
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="6">
         <v>0</v>
       </c>
-      <c r="G98" s="5" t="s">
-        <v>37</v>
+      <c r="G98" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4283,11 +4283,11 @@
       <c r="E99">
         <v>5</v>
       </c>
-      <c r="F99" s="4">
+      <c r="F99" s="6">
         <v>0</v>
       </c>
-      <c r="G99" s="5" t="s">
-        <v>37</v>
+      <c r="G99" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4398,11 +4398,11 @@
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F104" s="4">
         <v>4</v>
       </c>
-      <c r="G104" s="7" t="s">
-        <v>74</v>
+      <c r="G104" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4421,11 +4421,11 @@
       <c r="E105">
         <v>56</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="4">
         <v>354</v>
       </c>
-      <c r="G105" s="3" t="s">
-        <v>10</v>
+      <c r="G105" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4444,11 +4444,11 @@
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="4">
         <v>15</v>
       </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="G106" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4467,11 +4467,11 @@
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F107" s="4">
         <v>1</v>
       </c>
-      <c r="G107" s="7" t="s">
-        <v>74</v>
+      <c r="G107" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4490,11 +4490,11 @@
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="4">
         <v>79</v>
       </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="G108" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4513,11 +4513,11 @@
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="4">
+      <c r="F109" s="6">
         <v>0</v>
       </c>
-      <c r="G109" s="5" t="s">
-        <v>37</v>
+      <c r="G109" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4559,11 +4559,11 @@
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="6">
         <v>0</v>
       </c>
-      <c r="G111" s="5" t="s">
-        <v>37</v>
+      <c r="G111" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4582,11 +4582,11 @@
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="6">
         <v>0</v>
       </c>
-      <c r="G112" s="5" t="s">
-        <v>37</v>
+      <c r="G112" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4605,11 +4605,11 @@
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="6">
         <v>0</v>
       </c>
-      <c r="G113" s="5" t="s">
-        <v>37</v>
+      <c r="G113" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4628,11 +4628,11 @@
       <c r="E114">
         <v>5</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="4">
         <v>39</v>
       </c>
-      <c r="G114" s="3" t="s">
-        <v>10</v>
+      <c r="G114" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -4651,11 +4651,11 @@
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="4">
         <v>312</v>
       </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="G115" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4674,11 +4674,11 @@
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="4">
+      <c r="F116" s="6">
         <v>0</v>
       </c>
-      <c r="G116" s="5" t="s">
-        <v>37</v>
+      <c r="G116" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4697,11 +4697,11 @@
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="4">
         <v>2</v>
       </c>
-      <c r="G117" s="7" t="s">
-        <v>74</v>
+      <c r="G117" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4743,11 +4743,11 @@
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F119" s="4">
         <v>6</v>
       </c>
-      <c r="G119" s="7" t="s">
-        <v>74</v>
+      <c r="G119" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4766,11 +4766,11 @@
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="4">
         <v>36</v>
       </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="G120" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4789,11 +4789,11 @@
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="6">
         <v>0</v>
       </c>
-      <c r="G121" s="5" t="s">
-        <v>37</v>
+      <c r="G121" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4812,11 +4812,11 @@
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="4">
+      <c r="F122" s="6">
         <v>0</v>
       </c>
-      <c r="G122" s="5" t="s">
-        <v>37</v>
+      <c r="G122" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4835,11 +4835,11 @@
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="4">
         <v>127</v>
       </c>
-      <c r="G123" s="3" t="s">
-        <v>10</v>
+      <c r="G123" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4858,11 +4858,11 @@
       <c r="E124">
         <v>4</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="4">
         <v>37</v>
       </c>
-      <c r="G124" s="3" t="s">
-        <v>10</v>
+      <c r="G124" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -4881,11 +4881,11 @@
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="4">
+      <c r="F125" s="6">
         <v>0</v>
       </c>
-      <c r="G125" s="5" t="s">
-        <v>37</v>
+      <c r="G125" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4904,11 +4904,11 @@
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="4">
         <v>17</v>
       </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="G126" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4927,11 +4927,11 @@
       <c r="E127">
         <v>4</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="4">
         <v>24</v>
       </c>
-      <c r="G127" s="3" t="s">
-        <v>10</v>
+      <c r="G127" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -4950,11 +4950,11 @@
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="4">
         <v>18</v>
       </c>
-      <c r="G128" s="3" t="s">
-        <v>10</v>
+      <c r="G128" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4973,11 +4973,11 @@
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="6">
+      <c r="F129" s="4">
         <v>4</v>
       </c>
-      <c r="G129" s="7" t="s">
-        <v>74</v>
+      <c r="G129" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4996,11 +4996,11 @@
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="6">
+      <c r="F130" s="4">
         <v>3</v>
       </c>
-      <c r="G130" s="7" t="s">
-        <v>74</v>
+      <c r="G130" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5019,11 +5019,11 @@
       <c r="E131">
         <v>60</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="4">
         <v>357</v>
       </c>
-      <c r="G131" s="3" t="s">
-        <v>10</v>
+      <c r="G131" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5042,11 +5042,11 @@
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="4">
         <v>58</v>
       </c>
-      <c r="G132" s="3" t="s">
-        <v>10</v>
+      <c r="G132" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5065,11 +5065,11 @@
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="4">
         <v>138</v>
       </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="G133" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5088,11 +5088,11 @@
       <c r="E134">
         <v>60</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="4">
         <v>480</v>
       </c>
-      <c r="G134" s="3" t="s">
-        <v>10</v>
+      <c r="G134" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5111,11 +5111,11 @@
       <c r="E135">
         <v>60</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="4">
         <v>521</v>
       </c>
-      <c r="G135" s="3" t="s">
-        <v>10</v>
+      <c r="G135" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5134,11 +5134,11 @@
       <c r="E136">
         <v>60</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="4">
         <v>480</v>
       </c>
-      <c r="G136" s="3" t="s">
-        <v>10</v>
+      <c r="G136" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5203,11 +5203,11 @@
       <c r="E139">
         <v>63</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="4">
         <v>566</v>
       </c>
-      <c r="G139" s="3" t="s">
-        <v>10</v>
+      <c r="G139" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5249,11 +5249,11 @@
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="4">
         <v>108</v>
       </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="G141" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5272,11 +5272,11 @@
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="4">
         <v>122</v>
       </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="G142" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5295,11 +5295,11 @@
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="4">
         <v>15</v>
       </c>
-      <c r="G143" s="3" t="s">
-        <v>10</v>
+      <c r="G143" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5318,11 +5318,11 @@
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="4">
+      <c r="F144" s="6">
         <v>0</v>
       </c>
-      <c r="G144" s="5" t="s">
-        <v>37</v>
+      <c r="G144" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5341,11 +5341,11 @@
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="4">
         <v>10</v>
       </c>
-      <c r="G145" s="3" t="s">
-        <v>10</v>
+      <c r="G145" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5364,11 +5364,11 @@
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="4">
         <v>34</v>
       </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="G146" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5387,11 +5387,11 @@
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F147" s="6">
         <v>0</v>
       </c>
-      <c r="G147" s="5" t="s">
-        <v>37</v>
+      <c r="G147" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5410,11 +5410,11 @@
       <c r="E148">
         <v>5</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="4">
         <v>30</v>
       </c>
-      <c r="G148" s="3" t="s">
-        <v>10</v>
+      <c r="G148" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -5502,11 +5502,11 @@
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="6">
+      <c r="F152" s="4">
         <v>8</v>
       </c>
-      <c r="G152" s="7" t="s">
-        <v>74</v>
+      <c r="G152" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5525,11 +5525,11 @@
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="4">
         <v>640</v>
       </c>
-      <c r="G153" s="3" t="s">
-        <v>10</v>
+      <c r="G153" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5548,11 +5548,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="4">
         <v>121</v>
       </c>
-      <c r="G154" s="3" t="s">
-        <v>10</v>
+      <c r="G154" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5594,11 +5594,11 @@
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="4">
+      <c r="F156" s="6">
         <v>0</v>
       </c>
-      <c r="G156" s="5" t="s">
-        <v>37</v>
+      <c r="G156" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5617,11 +5617,11 @@
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="4">
         <v>66</v>
       </c>
-      <c r="G157" s="3" t="s">
-        <v>10</v>
+      <c r="G157" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5640,11 +5640,11 @@
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="4">
         <v>30</v>
       </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="G158" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5663,11 +5663,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="4">
         <v>83</v>
       </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="G159" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5686,11 +5686,11 @@
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="4">
         <v>10</v>
       </c>
-      <c r="G160" s="3" t="s">
-        <v>10</v>
+      <c r="G160" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5709,11 +5709,11 @@
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="4">
         <v>51</v>
       </c>
-      <c r="G161" s="3" t="s">
-        <v>10</v>
+      <c r="G161" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5732,11 +5732,11 @@
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="4">
         <v>74</v>
       </c>
-      <c r="G162" s="3" t="s">
-        <v>10</v>
+      <c r="G162" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5755,11 +5755,11 @@
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="4">
         <v>11</v>
       </c>
-      <c r="G163" s="3" t="s">
-        <v>10</v>
+      <c r="G163" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5778,11 +5778,11 @@
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="6">
+      <c r="F164" s="4">
         <v>4</v>
       </c>
-      <c r="G164" s="7" t="s">
-        <v>74</v>
+      <c r="G164" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5801,11 +5801,11 @@
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="4">
         <v>35</v>
       </c>
-      <c r="G165" s="3" t="s">
-        <v>10</v>
+      <c r="G165" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5824,11 +5824,11 @@
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="4">
         <v>62</v>
       </c>
-      <c r="G166" s="3" t="s">
-        <v>10</v>
+      <c r="G166" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5847,11 +5847,11 @@
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="4">
         <v>28</v>
       </c>
-      <c r="G167" s="3" t="s">
-        <v>10</v>
+      <c r="G167" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5870,11 +5870,11 @@
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="4">
         <v>920</v>
       </c>
-      <c r="G168" s="3" t="s">
-        <v>10</v>
+      <c r="G168" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5893,11 +5893,11 @@
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="4">
         <v>102</v>
       </c>
-      <c r="G169" s="3" t="s">
-        <v>10</v>
+      <c r="G169" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5916,11 +5916,11 @@
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="4">
         <v>211</v>
       </c>
-      <c r="G170" s="3" t="s">
-        <v>10</v>
+      <c r="G170" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5939,11 +5939,11 @@
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="4">
         <v>753</v>
       </c>
-      <c r="G171" s="3" t="s">
-        <v>10</v>
+      <c r="G171" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -5962,11 +5962,11 @@
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="4">
         <v>31</v>
       </c>
-      <c r="G172" s="3" t="s">
-        <v>10</v>
+      <c r="G172" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5985,11 +5985,11 @@
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="4">
         <v>93</v>
       </c>
-      <c r="G173" s="3" t="s">
-        <v>10</v>
+      <c r="G173" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6008,11 +6008,11 @@
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="4">
         <v>378</v>
       </c>
-      <c r="G174" s="3" t="s">
-        <v>10</v>
+      <c r="G174" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6031,11 +6031,11 @@
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="4">
         <v>94</v>
       </c>
-      <c r="G175" s="3" t="s">
-        <v>10</v>
+      <c r="G175" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6054,11 +6054,11 @@
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="2">
-        <v>103</v>
-      </c>
-      <c r="G176" s="3" t="s">
-        <v>10</v>
+      <c r="F176" s="4">
+        <v>103</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6077,11 +6077,11 @@
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="4">
         <v>93</v>
       </c>
-      <c r="G177" s="3" t="s">
-        <v>10</v>
+      <c r="G177" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6100,11 +6100,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="4">
         <v>68</v>
       </c>
-      <c r="G178" s="3" t="s">
-        <v>10</v>
+      <c r="G178" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6123,11 +6123,11 @@
       <c r="E179">
         <v>12</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="4">
         <v>77</v>
       </c>
-      <c r="G179" s="3" t="s">
-        <v>10</v>
+      <c r="G179" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6146,11 +6146,11 @@
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="4">
+      <c r="F180" s="6">
         <v>0</v>
       </c>
-      <c r="G180" s="5" t="s">
-        <v>37</v>
+      <c r="G180" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6169,11 +6169,11 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="6">
+      <c r="F181" s="4">
         <v>4</v>
       </c>
-      <c r="G181" s="7" t="s">
-        <v>74</v>
+      <c r="G181" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6192,11 +6192,11 @@
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="6">
+      <c r="F182" s="4">
         <v>6</v>
       </c>
-      <c r="G182" s="7" t="s">
-        <v>74</v>
+      <c r="G182" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6261,11 +6261,11 @@
       <c r="E185">
         <v>20</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="4">
         <v>144</v>
       </c>
-      <c r="G185" s="3" t="s">
-        <v>10</v>
+      <c r="G185" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -6284,11 +6284,11 @@
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="4">
         <v>40</v>
       </c>
-      <c r="G186" s="3" t="s">
-        <v>10</v>
+      <c r="G186" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6307,11 +6307,11 @@
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="4">
         <v>20</v>
       </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="G187" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6330,11 +6330,11 @@
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="4">
         <v>17</v>
       </c>
-      <c r="G188" s="3" t="s">
-        <v>10</v>
+      <c r="G188" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6353,11 +6353,11 @@
       <c r="E189">
         <v>50</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="4">
         <v>380</v>
       </c>
-      <c r="G189" s="3" t="s">
-        <v>10</v>
+      <c r="G189" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6491,11 +6491,11 @@
       <c r="E195">
         <v>60</v>
       </c>
-      <c r="F195" s="2">
+      <c r="F195" s="4">
         <v>454</v>
       </c>
-      <c r="G195" s="3" t="s">
-        <v>10</v>
+      <c r="G195" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6514,11 +6514,11 @@
       <c r="E196">
         <v>100</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="4">
         <v>880</v>
       </c>
-      <c r="G196" s="3" t="s">
-        <v>10</v>
+      <c r="G196" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">

--- a/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="515">
   <si>
     <t>#</t>
   </si>
@@ -43,7 +43,7 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
-    <t>✓ OK</t>
+    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>85007</t>
@@ -91,9 +91,6 @@
     <t>CUCHILLA ARTE AK-1/5B</t>
   </si>
   <si>
-    <t>⚠ BAJO</t>
-  </si>
-  <si>
     <t>85164</t>
   </si>
   <si>
@@ -127,9 +124,6 @@
     <t>CUCHILLLA DE ARTE AK-5/5B</t>
   </si>
   <si>
-    <t>✗ AGOTADO</t>
-  </si>
-  <si>
     <t>85166</t>
   </si>
   <si>
@@ -322,7 +316,7 @@
     <t>85863</t>
   </si>
   <si>
-    <t/>
+    <t>0</t>
   </si>
   <si>
     <t>CUCHILLA SEGURIDAD SK-4/24</t>
@@ -1568,7 +1562,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1586,21 +1580,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF065F46"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFD97706"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1610,16 +1594,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF13DAEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1640,7 +1614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1649,18 +1623,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2053,7 +2015,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>6770</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2076,7 +2038,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>27406</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2099,7 +2061,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="2">
-        <v>7881</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -2122,7 +2084,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20889</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2145,7 +2107,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>36483</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -2167,11 +2129,11 @@
       <c r="E7">
         <v>120</v>
       </c>
-      <c r="F7" s="4">
-        <v>1031</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>26</v>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2179,22 +2141,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
       </c>
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="4">
-        <v>268</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>26</v>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2202,22 +2164,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="4">
-        <v>253</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>26</v>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2225,22 +2187,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="4">
-        <v>59</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>26</v>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2248,22 +2210,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>38</v>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2271,22 +2233,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
         <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
       </c>
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="4">
-        <v>132</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>26</v>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2294,22 +2256,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
         <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
       </c>
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="4">
-        <v>191</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>26</v>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2317,22 +2279,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
         <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
       </c>
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="4">
-        <v>189</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>26</v>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2340,22 +2302,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
         <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
       </c>
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="4">
-        <v>84</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>26</v>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2363,22 +2325,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
         <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
       </c>
       <c r="E16">
         <v>120</v>
       </c>
-      <c r="F16" s="4">
-        <v>692</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>26</v>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2386,22 +2348,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
         <v>54</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>56</v>
       </c>
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="4">
-        <v>257</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>26</v>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2409,22 +2371,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
         <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" t="s">
-        <v>59</v>
       </c>
       <c r="E18">
         <v>120</v>
       </c>
-      <c r="F18" s="4">
-        <v>983</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>26</v>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2432,22 +2394,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
         <v>60</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
       </c>
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="4">
-        <v>195</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>26</v>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2455,22 +2417,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
         <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>65</v>
       </c>
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="4">
-        <v>75</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>26</v>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2478,22 +2440,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
         <v>66</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
       </c>
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="4">
-        <v>439</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>26</v>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2501,19 +2463,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
         <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
       </c>
       <c r="E22">
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>2053</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2524,22 +2486,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
         <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
       </c>
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="4">
-        <v>3</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>26</v>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2547,22 +2509,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
         <v>75</v>
-      </c>
-      <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" t="s">
-        <v>77</v>
       </c>
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="4">
-        <v>113</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>26</v>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2570,22 +2532,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
         <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>80</v>
       </c>
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="4">
-        <v>348</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>26</v>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2593,22 +2555,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
         <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" t="s">
-        <v>83</v>
       </c>
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="4">
-        <v>123</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>26</v>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2616,22 +2578,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" t="s">
         <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>86</v>
       </c>
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="4">
-        <v>160</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>26</v>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2639,19 +2601,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" t="s">
         <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>89</v>
       </c>
       <c r="E28">
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>9252</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2662,22 +2624,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" t="s">
         <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
       </c>
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="4">
-        <v>94</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>26</v>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2685,22 +2647,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="s">
         <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>95</v>
       </c>
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="4">
-        <v>56</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>26</v>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2708,19 +2670,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" t="s">
         <v>96</v>
-      </c>
-      <c r="C31" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" t="s">
-        <v>98</v>
       </c>
       <c r="E31">
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>3120</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -2731,19 +2693,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" t="s">
         <v>99</v>
-      </c>
-      <c r="C32" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" t="s">
-        <v>101</v>
       </c>
       <c r="E32">
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>1445</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2754,22 +2716,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" t="s">
         <v>102</v>
-      </c>
-      <c r="C33" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
       </c>
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>38</v>
+      <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2777,22 +2739,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" t="s">
         <v>105</v>
-      </c>
-      <c r="C34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
       </c>
       <c r="E34">
         <v>120</v>
       </c>
-      <c r="F34" s="4">
-        <v>907</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>26</v>
+      <c r="F34" s="2">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2800,22 +2762,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" t="s">
         <v>108</v>
-      </c>
-      <c r="C35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" t="s">
-        <v>110</v>
       </c>
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="6">
-        <v>0</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>38</v>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2823,22 +2785,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" t="s">
         <v>111</v>
-      </c>
-      <c r="C36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" t="s">
-        <v>113</v>
       </c>
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="4">
-        <v>118</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>26</v>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2846,22 +2808,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" t="s">
         <v>114</v>
-      </c>
-      <c r="C37" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" t="s">
-        <v>116</v>
       </c>
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="4">
-        <v>944</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>26</v>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2869,22 +2831,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" t="s">
         <v>117</v>
-      </c>
-      <c r="C38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" t="s">
-        <v>119</v>
       </c>
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="4">
-        <v>123</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>26</v>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2892,22 +2854,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" t="s">
         <v>120</v>
-      </c>
-      <c r="C39" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" t="s">
-        <v>122</v>
       </c>
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="4">
-        <v>278</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>26</v>
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2915,22 +2877,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" t="s">
         <v>123</v>
-      </c>
-      <c r="C40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
       </c>
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="4">
-        <v>245</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>26</v>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2938,22 +2900,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" t="s">
         <v>126</v>
-      </c>
-      <c r="C41" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" t="s">
-        <v>128</v>
       </c>
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="4">
-        <v>107</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>26</v>
+      <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2961,22 +2923,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="4">
-        <v>273</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>26</v>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2984,19 +2946,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" t="s">
         <v>131</v>
-      </c>
-      <c r="C43" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" t="s">
-        <v>133</v>
       </c>
       <c r="E43">
         <v>240</v>
       </c>
       <c r="F43" s="2">
-        <v>2865</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -3007,22 +2969,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" t="s">
         <v>134</v>
-      </c>
-      <c r="C44" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" t="s">
-        <v>136</v>
       </c>
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="4">
-        <v>1090</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>26</v>
+      <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3030,22 +2992,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" t="s">
         <v>137</v>
-      </c>
-      <c r="C45" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" t="s">
-        <v>139</v>
       </c>
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="4">
-        <v>163</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>26</v>
+      <c r="F45" s="2">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3053,22 +3015,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>139</v>
+      </c>
+      <c r="D46" t="s">
         <v>140</v>
-      </c>
-      <c r="C46" t="s">
-        <v>141</v>
-      </c>
-      <c r="D46" t="s">
-        <v>142</v>
       </c>
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="4">
-        <v>1475</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>26</v>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3076,22 +3038,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" t="s">
+        <v>142</v>
+      </c>
+      <c r="D47" t="s">
         <v>143</v>
-      </c>
-      <c r="C47" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" t="s">
-        <v>145</v>
       </c>
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="4">
-        <v>164</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>26</v>
+      <c r="F47" s="2">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3099,22 +3061,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="4">
-        <v>140</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>26</v>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3122,22 +3084,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" t="s">
         <v>148</v>
-      </c>
-      <c r="C49" t="s">
-        <v>149</v>
-      </c>
-      <c r="D49" t="s">
-        <v>150</v>
       </c>
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="4">
-        <v>261</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>26</v>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3145,22 +3107,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" t="s">
         <v>151</v>
-      </c>
-      <c r="C50" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50" t="s">
-        <v>153</v>
       </c>
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="4">
-        <v>291</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>26</v>
+      <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3168,22 +3130,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" t="s">
         <v>154</v>
       </c>
-      <c r="C51" t="s">
-        <v>155</v>
-      </c>
-      <c r="D51" t="s">
-        <v>156</v>
-      </c>
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="4">
-        <v>10</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>26</v>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3191,22 +3153,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" t="s">
+        <v>156</v>
+      </c>
+      <c r="D52" t="s">
         <v>157</v>
-      </c>
-      <c r="C52" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" t="s">
-        <v>159</v>
       </c>
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="4">
-        <v>82</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>26</v>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3214,22 +3176,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" t="s">
         <v>160</v>
-      </c>
-      <c r="C53" t="s">
-        <v>161</v>
-      </c>
-      <c r="D53" t="s">
-        <v>162</v>
       </c>
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="4">
-        <v>27</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>26</v>
+      <c r="F53" s="2">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3237,22 +3199,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" t="s">
         <v>163</v>
-      </c>
-      <c r="C54" t="s">
-        <v>164</v>
-      </c>
-      <c r="D54" t="s">
-        <v>165</v>
       </c>
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="4">
-        <v>2462</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>26</v>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3260,22 +3222,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" t="s">
         <v>166</v>
-      </c>
-      <c r="C55" t="s">
-        <v>167</v>
-      </c>
-      <c r="D55" t="s">
-        <v>168</v>
       </c>
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="4">
-        <v>208</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>26</v>
+      <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3283,22 +3245,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" t="s">
         <v>169</v>
-      </c>
-      <c r="C56" t="s">
-        <v>170</v>
-      </c>
-      <c r="D56" t="s">
-        <v>171</v>
       </c>
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="6">
-        <v>0</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>38</v>
+      <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3306,22 +3268,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" t="s">
         <v>172</v>
-      </c>
-      <c r="C57" t="s">
-        <v>173</v>
-      </c>
-      <c r="D57" t="s">
-        <v>174</v>
       </c>
       <c r="E57">
         <v>720</v>
       </c>
-      <c r="F57" s="4">
-        <v>4873</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>26</v>
+      <c r="F57" s="2">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3329,22 +3291,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" t="s">
+        <v>174</v>
+      </c>
+      <c r="D58" t="s">
         <v>175</v>
-      </c>
-      <c r="C58" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" t="s">
-        <v>177</v>
       </c>
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="4">
-        <v>201</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>26</v>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3352,22 +3314,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" t="s">
+        <v>177</v>
+      </c>
+      <c r="D59" t="s">
         <v>178</v>
-      </c>
-      <c r="C59" t="s">
-        <v>179</v>
-      </c>
-      <c r="D59" t="s">
-        <v>180</v>
       </c>
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="6">
-        <v>0</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>38</v>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3375,22 +3337,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D60" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="6">
-        <v>0</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>38</v>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3398,22 +3360,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" t="s">
         <v>183</v>
-      </c>
-      <c r="C61" t="s">
-        <v>184</v>
-      </c>
-      <c r="D61" t="s">
-        <v>185</v>
       </c>
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="4">
-        <v>300</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>26</v>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3421,22 +3383,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D62" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="4">
-        <v>198</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>26</v>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3444,19 +3406,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" t="s">
         <v>188</v>
-      </c>
-      <c r="C63" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" t="s">
-        <v>190</v>
       </c>
       <c r="E63">
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>7884</v>
+        <v>0</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3467,22 +3429,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" t="s">
         <v>191</v>
-      </c>
-      <c r="C64" t="s">
-        <v>192</v>
-      </c>
-      <c r="D64" t="s">
-        <v>193</v>
       </c>
       <c r="E64">
         <v>60</v>
       </c>
-      <c r="F64" s="4">
-        <v>513</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>26</v>
+      <c r="F64" s="2">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3490,22 +3452,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" t="s">
         <v>194</v>
-      </c>
-      <c r="C65" t="s">
-        <v>195</v>
-      </c>
-      <c r="D65" t="s">
-        <v>196</v>
       </c>
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="4">
-        <v>65</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>26</v>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3513,22 +3475,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>195</v>
+      </c>
+      <c r="C66" t="s">
+        <v>196</v>
+      </c>
+      <c r="D66" t="s">
         <v>197</v>
-      </c>
-      <c r="C66" t="s">
-        <v>198</v>
-      </c>
-      <c r="D66" t="s">
-        <v>199</v>
       </c>
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="4">
-        <v>69</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>26</v>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3536,22 +3498,22 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" t="s">
+        <v>199</v>
+      </c>
+      <c r="D67" t="s">
         <v>200</v>
-      </c>
-      <c r="C67" t="s">
-        <v>201</v>
-      </c>
-      <c r="D67" t="s">
-        <v>202</v>
       </c>
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="6">
-        <v>0</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>38</v>
+      <c r="F67" s="2">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3559,22 +3521,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>201</v>
+      </c>
+      <c r="C68" t="s">
+        <v>202</v>
+      </c>
+      <c r="D68" t="s">
         <v>203</v>
-      </c>
-      <c r="C68" t="s">
-        <v>204</v>
-      </c>
-      <c r="D68" t="s">
-        <v>205</v>
       </c>
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="4">
-        <v>55</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>26</v>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3582,19 +3544,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" t="s">
+        <v>205</v>
+      </c>
+      <c r="D69" t="s">
         <v>206</v>
-      </c>
-      <c r="C69" t="s">
-        <v>207</v>
-      </c>
-      <c r="D69" t="s">
-        <v>208</v>
       </c>
       <c r="E69">
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>4170</v>
+        <v>0</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3605,22 +3567,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>207</v>
+      </c>
+      <c r="C70" t="s">
+        <v>208</v>
+      </c>
+      <c r="D70" t="s">
         <v>209</v>
-      </c>
-      <c r="C70" t="s">
-        <v>210</v>
-      </c>
-      <c r="D70" t="s">
-        <v>211</v>
       </c>
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="4">
-        <v>130</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>26</v>
+      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3628,22 +3590,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>210</v>
+      </c>
+      <c r="C71" t="s">
+        <v>211</v>
+      </c>
+      <c r="D71" t="s">
         <v>212</v>
-      </c>
-      <c r="C71" t="s">
-        <v>213</v>
-      </c>
-      <c r="D71" t="s">
-        <v>214</v>
       </c>
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="6">
-        <v>0</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>38</v>
+      <c r="F71" s="2">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3651,22 +3613,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>213</v>
+      </c>
+      <c r="C72" t="s">
+        <v>214</v>
+      </c>
+      <c r="D72" t="s">
         <v>215</v>
-      </c>
-      <c r="C72" t="s">
-        <v>216</v>
-      </c>
-      <c r="D72" t="s">
-        <v>217</v>
       </c>
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="4">
-        <v>412</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>26</v>
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3674,22 +3636,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>216</v>
+      </c>
+      <c r="C73" t="s">
+        <v>217</v>
+      </c>
+      <c r="D73" t="s">
         <v>218</v>
-      </c>
-      <c r="C73" t="s">
-        <v>219</v>
-      </c>
-      <c r="D73" t="s">
-        <v>220</v>
       </c>
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="4">
-        <v>500</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>26</v>
+      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3697,22 +3659,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>219</v>
+      </c>
+      <c r="C74" t="s">
+        <v>220</v>
+      </c>
+      <c r="D74" t="s">
         <v>221</v>
-      </c>
-      <c r="C74" t="s">
-        <v>222</v>
-      </c>
-      <c r="D74" t="s">
-        <v>223</v>
       </c>
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="4">
-        <v>1529</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>26</v>
+      <c r="F74" s="2">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3720,19 +3682,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>222</v>
+      </c>
+      <c r="C75" t="s">
+        <v>223</v>
+      </c>
+      <c r="D75" t="s">
         <v>224</v>
-      </c>
-      <c r="C75" t="s">
-        <v>225</v>
-      </c>
-      <c r="D75" t="s">
-        <v>226</v>
       </c>
       <c r="E75">
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>4001</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3743,22 +3705,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76" t="s">
+        <v>226</v>
+      </c>
+      <c r="D76" t="s">
         <v>227</v>
-      </c>
-      <c r="C76" t="s">
-        <v>228</v>
-      </c>
-      <c r="D76" t="s">
-        <v>229</v>
       </c>
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="6">
-        <v>0</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>38</v>
+      <c r="F76" s="2">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3766,22 +3728,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D77" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="4">
-        <v>539</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>26</v>
+      <c r="F77" s="2">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3789,22 +3751,22 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C78" t="s">
+        <v>231</v>
+      </c>
+      <c r="D78" t="s">
         <v>232</v>
-      </c>
-      <c r="C78" t="s">
-        <v>233</v>
-      </c>
-      <c r="D78" t="s">
-        <v>234</v>
       </c>
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="4">
-        <v>114</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>26</v>
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3812,22 +3774,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>233</v>
+      </c>
+      <c r="C79" t="s">
+        <v>234</v>
+      </c>
+      <c r="D79" t="s">
         <v>235</v>
-      </c>
-      <c r="C79" t="s">
-        <v>236</v>
-      </c>
-      <c r="D79" t="s">
-        <v>237</v>
       </c>
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="4">
-        <v>4</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>26</v>
+      <c r="F79" s="2">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3835,22 +3797,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>236</v>
+      </c>
+      <c r="C80" t="s">
+        <v>237</v>
+      </c>
+      <c r="D80" t="s">
         <v>238</v>
-      </c>
-      <c r="C80" t="s">
-        <v>239</v>
-      </c>
-      <c r="D80" t="s">
-        <v>240</v>
       </c>
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="4">
-        <v>12</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>26</v>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3858,19 +3820,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>239</v>
+      </c>
+      <c r="C81" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" t="s">
         <v>241</v>
-      </c>
-      <c r="C81" t="s">
-        <v>242</v>
-      </c>
-      <c r="D81" t="s">
-        <v>243</v>
       </c>
       <c r="E81">
         <v>20</v>
       </c>
       <c r="F81" s="2">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -3881,19 +3843,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" t="s">
+        <v>243</v>
+      </c>
+      <c r="D82" t="s">
         <v>244</v>
-      </c>
-      <c r="C82" t="s">
-        <v>245</v>
-      </c>
-      <c r="D82" t="s">
-        <v>246</v>
       </c>
       <c r="E82">
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>2766</v>
+        <v>0</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -3904,22 +3866,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>245</v>
+      </c>
+      <c r="C83" t="s">
+        <v>246</v>
+      </c>
+      <c r="D83" t="s">
         <v>247</v>
-      </c>
-      <c r="C83" t="s">
-        <v>248</v>
-      </c>
-      <c r="D83" t="s">
-        <v>249</v>
       </c>
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="6">
-        <v>0</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>38</v>
+      <c r="F83" s="2">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3927,22 +3889,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84" t="s">
+        <v>249</v>
+      </c>
+      <c r="D84" t="s">
         <v>250</v>
-      </c>
-      <c r="C84" t="s">
-        <v>251</v>
-      </c>
-      <c r="D84" t="s">
-        <v>252</v>
       </c>
       <c r="E84">
         <v>40</v>
       </c>
-      <c r="F84" s="4">
-        <v>80</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>26</v>
+      <c r="F84" s="2">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3950,22 +3912,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>251</v>
+      </c>
+      <c r="C85" t="s">
+        <v>252</v>
+      </c>
+      <c r="D85" t="s">
         <v>253</v>
-      </c>
-      <c r="C85" t="s">
-        <v>254</v>
-      </c>
-      <c r="D85" t="s">
-        <v>255</v>
       </c>
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="6">
-        <v>0</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>38</v>
+      <c r="F85" s="2">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3973,22 +3935,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>254</v>
+      </c>
+      <c r="C86" t="s">
+        <v>255</v>
+      </c>
+      <c r="D86" t="s">
         <v>256</v>
-      </c>
-      <c r="C86" t="s">
-        <v>257</v>
-      </c>
-      <c r="D86" t="s">
-        <v>258</v>
       </c>
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="6">
-        <v>0</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>38</v>
+      <c r="F86" s="2">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -3996,22 +3958,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>257</v>
+      </c>
+      <c r="C87" t="s">
+        <v>258</v>
+      </c>
+      <c r="D87" t="s">
         <v>259</v>
-      </c>
-      <c r="C87" t="s">
-        <v>260</v>
-      </c>
-      <c r="D87" t="s">
-        <v>261</v>
       </c>
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="6">
-        <v>0</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>38</v>
+      <c r="F87" s="2">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4019,22 +3981,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>260</v>
+      </c>
+      <c r="C88" t="s">
+        <v>261</v>
+      </c>
+      <c r="D88" t="s">
         <v>262</v>
-      </c>
-      <c r="C88" t="s">
-        <v>263</v>
-      </c>
-      <c r="D88" t="s">
-        <v>264</v>
       </c>
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="6">
-        <v>0</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>38</v>
+      <c r="F88" s="2">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4042,19 +4004,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" t="s">
+        <v>264</v>
+      </c>
+      <c r="D89" t="s">
         <v>265</v>
-      </c>
-      <c r="C89" t="s">
-        <v>266</v>
-      </c>
-      <c r="D89" t="s">
-        <v>267</v>
       </c>
       <c r="E89">
         <v>20</v>
       </c>
       <c r="F89" s="2">
-        <v>1473</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -4065,19 +4027,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>266</v>
+      </c>
+      <c r="C90" t="s">
+        <v>267</v>
+      </c>
+      <c r="D90" t="s">
         <v>268</v>
-      </c>
-      <c r="C90" t="s">
-        <v>269</v>
-      </c>
-      <c r="D90" t="s">
-        <v>270</v>
       </c>
       <c r="E90">
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>108017</v>
+        <v>0</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4088,22 +4050,22 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>269</v>
+      </c>
+      <c r="C91" t="s">
+        <v>270</v>
+      </c>
+      <c r="D91" t="s">
         <v>271</v>
       </c>
-      <c r="C91" t="s">
-        <v>272</v>
-      </c>
-      <c r="D91" t="s">
-        <v>273</v>
-      </c>
       <c r="E91">
         <v>10</v>
       </c>
-      <c r="F91" s="4">
-        <v>68</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>26</v>
+      <c r="F91" s="2">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4111,19 +4073,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>272</v>
+      </c>
+      <c r="C92" t="s">
+        <v>273</v>
+      </c>
+      <c r="D92" t="s">
         <v>274</v>
       </c>
-      <c r="C92" t="s">
-        <v>275</v>
-      </c>
-      <c r="D92" t="s">
-        <v>276</v>
-      </c>
       <c r="E92">
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4134,19 +4096,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" t="s">
+        <v>276</v>
+      </c>
+      <c r="D93" t="s">
         <v>277</v>
-      </c>
-      <c r="C93" t="s">
-        <v>278</v>
-      </c>
-      <c r="D93" t="s">
-        <v>279</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4157,19 +4119,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C94" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D94" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E94">
         <v>6</v>
       </c>
       <c r="F94" s="2">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4180,22 +4142,22 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>280</v>
+      </c>
+      <c r="C95" t="s">
+        <v>281</v>
+      </c>
+      <c r="D95" t="s">
         <v>282</v>
-      </c>
-      <c r="C95" t="s">
-        <v>283</v>
-      </c>
-      <c r="D95" t="s">
-        <v>284</v>
       </c>
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="6">
-        <v>0</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>38</v>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4203,22 +4165,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D96" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="6">
-        <v>0</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>38</v>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4226,22 +4188,22 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>285</v>
+      </c>
+      <c r="C97" t="s">
+        <v>286</v>
+      </c>
+      <c r="D97" t="s">
         <v>287</v>
       </c>
-      <c r="C97" t="s">
-        <v>288</v>
-      </c>
-      <c r="D97" t="s">
-        <v>289</v>
-      </c>
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="4">
-        <v>7</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>26</v>
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4249,22 +4211,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>288</v>
+      </c>
+      <c r="C98" t="s">
+        <v>289</v>
+      </c>
+      <c r="D98" t="s">
         <v>290</v>
-      </c>
-      <c r="C98" t="s">
-        <v>291</v>
-      </c>
-      <c r="D98" t="s">
-        <v>292</v>
       </c>
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="6">
-        <v>0</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>38</v>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4272,22 +4234,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>291</v>
+      </c>
+      <c r="C99" t="s">
+        <v>292</v>
+      </c>
+      <c r="D99" t="s">
         <v>293</v>
-      </c>
-      <c r="C99" t="s">
-        <v>294</v>
-      </c>
-      <c r="D99" t="s">
-        <v>295</v>
       </c>
       <c r="E99">
         <v>5</v>
       </c>
-      <c r="F99" s="6">
-        <v>0</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>38</v>
+      <c r="F99" s="2">
+        <v>0</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4295,19 +4257,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>294</v>
+      </c>
+      <c r="C100" t="s">
+        <v>295</v>
+      </c>
+      <c r="D100" t="s">
         <v>296</v>
-      </c>
-      <c r="C100" t="s">
-        <v>297</v>
-      </c>
-      <c r="D100" t="s">
-        <v>298</v>
       </c>
       <c r="E100">
         <v>6</v>
       </c>
       <c r="F100" s="2">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4318,19 +4280,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>297</v>
+      </c>
+      <c r="C101" t="s">
+        <v>298</v>
+      </c>
+      <c r="D101" t="s">
         <v>299</v>
-      </c>
-      <c r="C101" t="s">
-        <v>300</v>
-      </c>
-      <c r="D101" t="s">
-        <v>301</v>
       </c>
       <c r="E101">
         <v>6</v>
       </c>
       <c r="F101" s="2">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4341,19 +4303,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>300</v>
+      </c>
+      <c r="C102" t="s">
+        <v>301</v>
+      </c>
+      <c r="D102" t="s">
         <v>302</v>
-      </c>
-      <c r="C102" t="s">
-        <v>303</v>
-      </c>
-      <c r="D102" t="s">
-        <v>304</v>
       </c>
       <c r="E102">
         <v>6</v>
       </c>
       <c r="F102" s="2">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4364,19 +4326,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>303</v>
+      </c>
+      <c r="C103" t="s">
+        <v>304</v>
+      </c>
+      <c r="D103" t="s">
         <v>305</v>
-      </c>
-      <c r="C103" t="s">
-        <v>306</v>
-      </c>
-      <c r="D103" t="s">
-        <v>307</v>
       </c>
       <c r="E103">
         <v>6</v>
       </c>
       <c r="F103" s="2">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>10</v>
@@ -4387,22 +4349,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>306</v>
+      </c>
+      <c r="C104" t="s">
+        <v>307</v>
+      </c>
+      <c r="D104" t="s">
         <v>308</v>
-      </c>
-      <c r="C104" t="s">
-        <v>309</v>
-      </c>
-      <c r="D104" t="s">
-        <v>310</v>
       </c>
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="4">
-        <v>4</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>26</v>
+      <c r="F104" s="2">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4410,22 +4372,22 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>309</v>
+      </c>
+      <c r="C105" t="s">
+        <v>310</v>
+      </c>
+      <c r="D105" t="s">
         <v>311</v>
-      </c>
-      <c r="C105" t="s">
-        <v>312</v>
-      </c>
-      <c r="D105" t="s">
-        <v>313</v>
       </c>
       <c r="E105">
         <v>56</v>
       </c>
-      <c r="F105" s="4">
-        <v>354</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>26</v>
+      <c r="F105" s="2">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4433,22 +4395,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>312</v>
+      </c>
+      <c r="C106" t="s">
+        <v>313</v>
+      </c>
+      <c r="D106" t="s">
         <v>314</v>
-      </c>
-      <c r="C106" t="s">
-        <v>315</v>
-      </c>
-      <c r="D106" t="s">
-        <v>316</v>
       </c>
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="4">
-        <v>15</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>26</v>
+      <c r="F106" s="2">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4456,22 +4418,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>315</v>
+      </c>
+      <c r="C107" t="s">
+        <v>316</v>
+      </c>
+      <c r="D107" t="s">
         <v>317</v>
-      </c>
-      <c r="C107" t="s">
-        <v>318</v>
-      </c>
-      <c r="D107" t="s">
-        <v>319</v>
       </c>
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="4">
-        <v>1</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>26</v>
+      <c r="F107" s="2">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4479,22 +4441,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>318</v>
+      </c>
+      <c r="C108" t="s">
+        <v>319</v>
+      </c>
+      <c r="D108" t="s">
         <v>320</v>
-      </c>
-      <c r="C108" t="s">
-        <v>321</v>
-      </c>
-      <c r="D108" t="s">
-        <v>322</v>
       </c>
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="4">
-        <v>79</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>26</v>
+      <c r="F108" s="2">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4502,22 +4464,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C109" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D109" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="6">
-        <v>0</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>38</v>
+      <c r="F109" s="2">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4525,19 +4487,19 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>323</v>
+      </c>
+      <c r="C110" t="s">
+        <v>324</v>
+      </c>
+      <c r="D110" t="s">
         <v>325</v>
-      </c>
-      <c r="C110" t="s">
-        <v>326</v>
-      </c>
-      <c r="D110" t="s">
-        <v>327</v>
       </c>
       <c r="E110">
         <v>54</v>
       </c>
       <c r="F110" s="2">
-        <v>1093</v>
+        <v>0</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4548,22 +4510,22 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D111" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="6">
-        <v>0</v>
-      </c>
-      <c r="G111" s="7" t="s">
-        <v>38</v>
+      <c r="F111" s="2">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4571,22 +4533,22 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C112" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D112" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="6">
-        <v>0</v>
-      </c>
-      <c r="G112" s="7" t="s">
-        <v>38</v>
+      <c r="F112" s="2">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4594,22 +4556,22 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C113" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D113" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="6">
-        <v>0</v>
-      </c>
-      <c r="G113" s="7" t="s">
-        <v>38</v>
+      <c r="F113" s="2">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4617,22 +4579,22 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C114" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D114" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E114">
         <v>5</v>
       </c>
-      <c r="F114" s="4">
-        <v>39</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>26</v>
+      <c r="F114" s="2">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -4640,22 +4602,22 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C115" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D115" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="4">
-        <v>312</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>26</v>
+      <c r="F115" s="2">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4663,22 +4625,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C116" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D116" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="6">
-        <v>0</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>38</v>
+      <c r="F116" s="2">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4686,22 +4648,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C117" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D117" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="4">
-        <v>2</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>26</v>
+      <c r="F117" s="2">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4709,19 +4671,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C118" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D118" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E118">
         <v>10</v>
       </c>
       <c r="F118" s="2">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -4732,22 +4694,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C119" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D119" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="4">
-        <v>6</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>26</v>
+      <c r="F119" s="2">
+        <v>0</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4755,22 +4717,22 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C120" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D120" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="4">
-        <v>36</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>26</v>
+      <c r="F120" s="2">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4778,22 +4740,22 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C121" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D121" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="6">
-        <v>0</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>38</v>
+      <c r="F121" s="2">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4801,22 +4763,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C122" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D122" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="6">
-        <v>0</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>38</v>
+      <c r="F122" s="2">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4824,22 +4786,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C123" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D123" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="4">
-        <v>127</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>26</v>
+      <c r="F123" s="2">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4847,22 +4809,22 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C124" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D124" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E124">
         <v>4</v>
       </c>
-      <c r="F124" s="4">
-        <v>37</v>
-      </c>
-      <c r="G124" s="5" t="s">
-        <v>26</v>
+      <c r="F124" s="2">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -4870,22 +4832,22 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
+        <v>354</v>
+      </c>
+      <c r="C125" t="s">
+        <v>355</v>
+      </c>
+      <c r="D125" t="s">
         <v>356</v>
-      </c>
-      <c r="C125" t="s">
-        <v>357</v>
-      </c>
-      <c r="D125" t="s">
-        <v>358</v>
       </c>
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="6">
-        <v>0</v>
-      </c>
-      <c r="G125" s="7" t="s">
-        <v>38</v>
+      <c r="F125" s="2">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4893,22 +4855,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C126" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D126" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="4">
-        <v>17</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>26</v>
+      <c r="F126" s="2">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4916,22 +4878,22 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C127" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D127" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E127">
         <v>4</v>
       </c>
-      <c r="F127" s="4">
-        <v>24</v>
-      </c>
-      <c r="G127" s="5" t="s">
-        <v>26</v>
+      <c r="F127" s="2">
+        <v>0</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -4939,22 +4901,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C128" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D128" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="4">
-        <v>18</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>26</v>
+      <c r="F128" s="2">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4962,22 +4924,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C129" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D129" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="4">
-        <v>4</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>26</v>
+      <c r="F129" s="2">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4985,22 +4947,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C130" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D130" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="4">
-        <v>3</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>26</v>
+      <c r="F130" s="2">
+        <v>0</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5008,22 +4970,22 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D131" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E131">
         <v>60</v>
       </c>
-      <c r="F131" s="4">
-        <v>357</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>26</v>
+      <c r="F131" s="2">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5031,22 +4993,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C132" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D132" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="4">
-        <v>58</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>26</v>
+      <c r="F132" s="2">
+        <v>0</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5054,22 +5016,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C133" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D133" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="4">
-        <v>138</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>26</v>
+      <c r="F133" s="2">
+        <v>0</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5077,22 +5039,22 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C134" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D134" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E134">
         <v>60</v>
       </c>
-      <c r="F134" s="4">
-        <v>480</v>
-      </c>
-      <c r="G134" s="5" t="s">
-        <v>26</v>
+      <c r="F134" s="2">
+        <v>0</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5100,22 +5062,22 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C135" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E135">
         <v>60</v>
       </c>
-      <c r="F135" s="4">
-        <v>521</v>
-      </c>
-      <c r="G135" s="5" t="s">
-        <v>26</v>
+      <c r="F135" s="2">
+        <v>0</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5123,22 +5085,22 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C136" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D136" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E136">
         <v>60</v>
       </c>
-      <c r="F136" s="4">
-        <v>480</v>
-      </c>
-      <c r="G136" s="5" t="s">
-        <v>26</v>
+      <c r="F136" s="2">
+        <v>0</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5146,19 +5108,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C137" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E137">
         <v>30</v>
       </c>
       <c r="F137" s="2">
-        <v>1601</v>
+        <v>0</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>10</v>
@@ -5169,19 +5131,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C138" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E138">
         <v>40</v>
       </c>
       <c r="F138" s="2">
-        <v>1130</v>
+        <v>0</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>10</v>
@@ -5192,22 +5154,22 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C139" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E139">
         <v>63</v>
       </c>
-      <c r="F139" s="4">
-        <v>566</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>26</v>
+      <c r="F139" s="2">
+        <v>0</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5215,19 +5177,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C140" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E140">
         <v>10</v>
       </c>
       <c r="F140" s="2">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>10</v>
@@ -5238,22 +5200,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C141" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="4">
-        <v>108</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>26</v>
+      <c r="F141" s="2">
+        <v>0</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5261,22 +5223,22 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C142" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="4">
-        <v>122</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>26</v>
+      <c r="F142" s="2">
+        <v>0</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5284,22 +5246,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C143" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D143" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="4">
-        <v>15</v>
-      </c>
-      <c r="G143" s="5" t="s">
-        <v>26</v>
+      <c r="F143" s="2">
+        <v>0</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5307,22 +5269,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C144" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D144" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="6">
-        <v>0</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>38</v>
+      <c r="F144" s="2">
+        <v>0</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5330,22 +5292,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C145" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D145" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="4">
-        <v>10</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>26</v>
+      <c r="F145" s="2">
+        <v>0</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5353,22 +5315,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C146" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D146" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="4">
-        <v>34</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>26</v>
+      <c r="F146" s="2">
+        <v>0</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5376,22 +5338,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C147" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D147" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="6">
-        <v>0</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>38</v>
+      <c r="F147" s="2">
+        <v>0</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5399,22 +5361,22 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C148" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D148" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E148">
         <v>5</v>
       </c>
-      <c r="F148" s="4">
-        <v>30</v>
-      </c>
-      <c r="G148" s="5" t="s">
-        <v>26</v>
+      <c r="F148" s="2">
+        <v>0</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -5422,19 +5384,19 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C149" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E149">
         <v>5</v>
       </c>
       <c r="F149" s="2">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>10</v>
@@ -5445,19 +5407,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C150" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D150" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E150">
         <v>5</v>
       </c>
       <c r="F150" s="2">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -5468,19 +5430,19 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C151" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D151" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151" s="2">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5491,22 +5453,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C152" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D152" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="4">
-        <v>8</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>26</v>
+      <c r="F152" s="2">
+        <v>0</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5514,22 +5476,22 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C153" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="4">
-        <v>640</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>26</v>
+      <c r="F153" s="2">
+        <v>0</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5537,22 +5499,22 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>413</v>
+      </c>
+      <c r="C154" t="s">
+        <v>414</v>
+      </c>
+      <c r="D154" t="s">
         <v>415</v>
-      </c>
-      <c r="C154" t="s">
-        <v>416</v>
-      </c>
-      <c r="D154" t="s">
-        <v>417</v>
       </c>
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="4">
-        <v>121</v>
-      </c>
-      <c r="G154" s="5" t="s">
-        <v>26</v>
+      <c r="F154" s="2">
+        <v>0</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5560,19 +5522,19 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C155" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E155">
         <v>60</v>
       </c>
       <c r="F155" s="2">
-        <v>855</v>
+        <v>0</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>10</v>
@@ -5583,22 +5545,22 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C156" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D156" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="6">
-        <v>0</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>38</v>
+      <c r="F156" s="2">
+        <v>0</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5606,22 +5568,22 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>420</v>
+      </c>
+      <c r="C157" t="s">
+        <v>421</v>
+      </c>
+      <c r="D157" t="s">
         <v>422</v>
-      </c>
-      <c r="C157" t="s">
-        <v>423</v>
-      </c>
-      <c r="D157" t="s">
-        <v>424</v>
       </c>
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="4">
-        <v>66</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>26</v>
+      <c r="F157" s="2">
+        <v>0</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5629,22 +5591,22 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C158" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="4">
-        <v>30</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>26</v>
+      <c r="F158" s="2">
+        <v>0</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5652,22 +5614,22 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>425</v>
+      </c>
+      <c r="C159" t="s">
+        <v>426</v>
+      </c>
+      <c r="D159" t="s">
         <v>427</v>
-      </c>
-      <c r="C159" t="s">
-        <v>428</v>
-      </c>
-      <c r="D159" t="s">
-        <v>429</v>
       </c>
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="4">
-        <v>83</v>
-      </c>
-      <c r="G159" s="5" t="s">
-        <v>26</v>
+      <c r="F159" s="2">
+        <v>0</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5675,22 +5637,22 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>428</v>
+      </c>
+      <c r="C160" t="s">
+        <v>429</v>
+      </c>
+      <c r="D160" t="s">
         <v>430</v>
-      </c>
-      <c r="C160" t="s">
-        <v>431</v>
-      </c>
-      <c r="D160" t="s">
-        <v>432</v>
       </c>
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="4">
-        <v>10</v>
-      </c>
-      <c r="G160" s="5" t="s">
-        <v>26</v>
+      <c r="F160" s="2">
+        <v>0</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5698,22 +5660,22 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C161" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D161" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="4">
-        <v>51</v>
-      </c>
-      <c r="G161" s="5" t="s">
-        <v>26</v>
+      <c r="F161" s="2">
+        <v>0</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5721,22 +5683,22 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C162" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D162" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="4">
-        <v>74</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>26</v>
+      <c r="F162" s="2">
+        <v>0</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5744,22 +5706,22 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C163" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D163" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="4">
-        <v>11</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>26</v>
+      <c r="F163" s="2">
+        <v>0</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5767,22 +5729,22 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C164" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D164" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="4">
-        <v>4</v>
-      </c>
-      <c r="G164" s="5" t="s">
-        <v>26</v>
+      <c r="F164" s="2">
+        <v>0</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5790,22 +5752,22 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C165" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D165" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="4">
-        <v>35</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>26</v>
+      <c r="F165" s="2">
+        <v>0</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5813,22 +5775,22 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>441</v>
+      </c>
+      <c r="C166" t="s">
+        <v>442</v>
+      </c>
+      <c r="D166" t="s">
         <v>443</v>
-      </c>
-      <c r="C166" t="s">
-        <v>444</v>
-      </c>
-      <c r="D166" t="s">
-        <v>445</v>
       </c>
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="4">
-        <v>62</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>26</v>
+      <c r="F166" s="2">
+        <v>0</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5836,22 +5798,22 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>444</v>
+      </c>
+      <c r="C167" t="s">
+        <v>445</v>
+      </c>
+      <c r="D167" t="s">
         <v>446</v>
-      </c>
-      <c r="C167" t="s">
-        <v>447</v>
-      </c>
-      <c r="D167" t="s">
-        <v>448</v>
       </c>
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="4">
-        <v>28</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>26</v>
+      <c r="F167" s="2">
+        <v>0</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5859,22 +5821,22 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C168" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D168" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="4">
-        <v>920</v>
-      </c>
-      <c r="G168" s="5" t="s">
-        <v>26</v>
+      <c r="F168" s="2">
+        <v>0</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5882,22 +5844,22 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C169" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D169" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="4">
-        <v>102</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>26</v>
+      <c r="F169" s="2">
+        <v>0</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5905,22 +5867,22 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C170" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D170" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="4">
-        <v>211</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>26</v>
+      <c r="F170" s="2">
+        <v>0</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5928,22 +5890,22 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C171" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D171" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="4">
-        <v>753</v>
-      </c>
-      <c r="G171" s="5" t="s">
-        <v>26</v>
+      <c r="F171" s="2">
+        <v>0</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -5951,22 +5913,22 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C172" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D172" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="4">
-        <v>31</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>26</v>
+      <c r="F172" s="2">
+        <v>0</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5974,22 +5936,22 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C173" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D173" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="4">
-        <v>93</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>26</v>
+      <c r="F173" s="2">
+        <v>0</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -5997,22 +5959,22 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C174" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D174" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="4">
-        <v>378</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>26</v>
+      <c r="F174" s="2">
+        <v>0</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6020,22 +5982,22 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C175" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D175" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="4">
-        <v>94</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>26</v>
+      <c r="F175" s="2">
+        <v>0</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6043,22 +6005,22 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
+        <v>463</v>
+      </c>
+      <c r="C176" t="s">
+        <v>464</v>
+      </c>
+      <c r="D176" t="s">
         <v>465</v>
-      </c>
-      <c r="C176" t="s">
-        <v>466</v>
-      </c>
-      <c r="D176" t="s">
-        <v>467</v>
       </c>
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="4">
-        <v>103</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>26</v>
+      <c r="F176" s="2">
+        <v>0</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6066,22 +6028,22 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
+        <v>466</v>
+      </c>
+      <c r="C177" t="s">
+        <v>467</v>
+      </c>
+      <c r="D177" t="s">
         <v>468</v>
-      </c>
-      <c r="C177" t="s">
-        <v>469</v>
-      </c>
-      <c r="D177" t="s">
-        <v>470</v>
       </c>
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="4">
-        <v>93</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>26</v>
+      <c r="F177" s="2">
+        <v>0</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6089,22 +6051,22 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C178" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D178" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="4">
-        <v>68</v>
-      </c>
-      <c r="G178" s="5" t="s">
-        <v>26</v>
+      <c r="F178" s="2">
+        <v>0</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6112,22 +6074,22 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C179" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D179" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E179">
         <v>12</v>
       </c>
-      <c r="F179" s="4">
-        <v>77</v>
-      </c>
-      <c r="G179" s="5" t="s">
-        <v>26</v>
+      <c r="F179" s="2">
+        <v>0</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6135,22 +6097,22 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C180" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D180" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="6">
-        <v>0</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>38</v>
+      <c r="F180" s="2">
+        <v>0</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6158,22 +6120,22 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C181" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D181" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="4">
-        <v>4</v>
-      </c>
-      <c r="G181" s="5" t="s">
-        <v>26</v>
+      <c r="F181" s="2">
+        <v>0</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6181,22 +6143,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C182" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D182" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="4">
-        <v>6</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>26</v>
+      <c r="F182" s="2">
+        <v>0</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6204,19 +6166,19 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C183" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D183" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E183">
         <v>1</v>
       </c>
       <c r="F183" s="2">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>10</v>
@@ -6227,19 +6189,19 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C184" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D184" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E184">
         <v>20</v>
       </c>
       <c r="F184" s="2">
-        <v>3763</v>
+        <v>0</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>10</v>
@@ -6250,22 +6212,22 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C185" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D185" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E185">
         <v>20</v>
       </c>
-      <c r="F185" s="4">
-        <v>144</v>
-      </c>
-      <c r="G185" s="5" t="s">
-        <v>26</v>
+      <c r="F185" s="2">
+        <v>0</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -6273,22 +6235,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C186" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D186" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="4">
-        <v>40</v>
-      </c>
-      <c r="G186" s="5" t="s">
-        <v>26</v>
+      <c r="F186" s="2">
+        <v>0</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6296,22 +6258,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C187" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D187" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="4">
-        <v>20</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>26</v>
+      <c r="F187" s="2">
+        <v>0</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6319,22 +6281,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C188" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D188" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="4">
-        <v>17</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>26</v>
+      <c r="F188" s="2">
+        <v>0</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6342,22 +6304,22 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C189" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D189" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E189">
         <v>50</v>
       </c>
-      <c r="F189" s="4">
-        <v>380</v>
-      </c>
-      <c r="G189" s="5" t="s">
-        <v>26</v>
+      <c r="F189" s="2">
+        <v>0</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6365,19 +6327,19 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C190" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D190" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E190">
         <v>50</v>
       </c>
       <c r="F190" s="2">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -6388,19 +6350,19 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>495</v>
+      </c>
+      <c r="C191" t="s">
+        <v>496</v>
+      </c>
+      <c r="D191" t="s">
         <v>497</v>
-      </c>
-      <c r="C191" t="s">
-        <v>498</v>
-      </c>
-      <c r="D191" t="s">
-        <v>499</v>
       </c>
       <c r="E191">
         <v>50</v>
       </c>
       <c r="F191" s="2">
-        <v>1873</v>
+        <v>0</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6411,19 +6373,19 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>498</v>
+      </c>
+      <c r="C192" t="s">
+        <v>499</v>
+      </c>
+      <c r="D192" t="s">
         <v>500</v>
-      </c>
-      <c r="C192" t="s">
-        <v>501</v>
-      </c>
-      <c r="D192" t="s">
-        <v>502</v>
       </c>
       <c r="E192">
         <v>50</v>
       </c>
       <c r="F192" s="2">
-        <v>1210</v>
+        <v>0</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6434,19 +6396,19 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>501</v>
+      </c>
+      <c r="C193" t="s">
+        <v>502</v>
+      </c>
+      <c r="D193" t="s">
         <v>503</v>
-      </c>
-      <c r="C193" t="s">
-        <v>504</v>
-      </c>
-      <c r="D193" t="s">
-        <v>505</v>
       </c>
       <c r="E193">
         <v>50</v>
       </c>
       <c r="F193" s="2">
-        <v>19771</v>
+        <v>0</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6457,19 +6419,19 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>504</v>
+      </c>
+      <c r="C194" t="s">
+        <v>505</v>
+      </c>
+      <c r="D194" t="s">
         <v>506</v>
-      </c>
-      <c r="C194" t="s">
-        <v>507</v>
-      </c>
-      <c r="D194" t="s">
-        <v>508</v>
       </c>
       <c r="E194">
         <v>100</v>
       </c>
       <c r="F194" s="2">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
@@ -6480,22 +6442,22 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
+        <v>507</v>
+      </c>
+      <c r="C195" t="s">
+        <v>508</v>
+      </c>
+      <c r="D195" t="s">
         <v>509</v>
-      </c>
-      <c r="C195" t="s">
-        <v>510</v>
-      </c>
-      <c r="D195" t="s">
-        <v>511</v>
       </c>
       <c r="E195">
         <v>60</v>
       </c>
-      <c r="F195" s="4">
-        <v>454</v>
-      </c>
-      <c r="G195" s="5" t="s">
-        <v>26</v>
+      <c r="F195" s="2">
+        <v>0</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6503,22 +6465,22 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C196" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D196" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E196">
         <v>100</v>
       </c>
-      <c r="F196" s="4">
-        <v>880</v>
-      </c>
-      <c r="G196" s="5" t="s">
-        <v>26</v>
+      <c r="F196" s="2">
+        <v>0</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6526,19 +6488,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
+        <v>512</v>
+      </c>
+      <c r="C197" t="s">
+        <v>513</v>
+      </c>
+      <c r="D197" t="s">
         <v>514</v>
-      </c>
-      <c r="C197" t="s">
-        <v>515</v>
-      </c>
-      <c r="D197" t="s">
-        <v>516</v>
       </c>
       <c r="E197">
         <v>80</v>
       </c>
       <c r="F197" s="2">
-        <v>1247</v>
+        <v>0</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="517">
   <si>
     <t>#</t>
   </si>
@@ -43,85 +43,91 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
+    <t>✓ OK</t>
+  </si>
+  <si>
+    <t>85007</t>
+  </si>
+  <si>
+    <t>7754807850063</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85768</t>
+  </si>
+  <si>
+    <t>7754807857680</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85008</t>
+  </si>
+  <si>
+    <t>7754807850087</t>
+  </si>
+  <si>
+    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85801</t>
+  </si>
+  <si>
+    <t>7754807857024</t>
+  </si>
+  <si>
+    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
+  </si>
+  <si>
+    <t>85163</t>
+  </si>
+  <si>
+    <t>091511400595</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-1/5B</t>
+  </si>
+  <si>
+    <t>⚠ BAJO</t>
+  </si>
+  <si>
+    <t>85164</t>
+  </si>
+  <si>
+    <t>091511400670</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-4</t>
+  </si>
+  <si>
+    <t>85770</t>
+  </si>
+  <si>
+    <t>091511220292</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-5 + KB-5/30B</t>
+  </si>
+  <si>
+    <t>85868</t>
+  </si>
+  <si>
+    <t>4901165202925</t>
+  </si>
+  <si>
+    <t>CUCHILLLA ARTE AK-5 PINK</t>
+  </si>
+  <si>
+    <t>85871</t>
+  </si>
+  <si>
+    <t>CUCHILLLA DE ARTE AK-5/5B</t>
+  </si>
+  <si>
     <t>✗ AGOTADO</t>
-  </si>
-  <si>
-    <t>85007</t>
-  </si>
-  <si>
-    <t>7754807850063</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85768</t>
-  </si>
-  <si>
-    <t>7754807857680</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85008</t>
-  </si>
-  <si>
-    <t>7754807850087</t>
-  </si>
-  <si>
-    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85801</t>
-  </si>
-  <si>
-    <t>7754807857024</t>
-  </si>
-  <si>
-    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
-  </si>
-  <si>
-    <t>85163</t>
-  </si>
-  <si>
-    <t>091511400595</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-1/5B</t>
-  </si>
-  <si>
-    <t>85164</t>
-  </si>
-  <si>
-    <t>091511400670</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-4</t>
-  </si>
-  <si>
-    <t>85770</t>
-  </si>
-  <si>
-    <t>091511220292</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-5 + KB-5/30B</t>
-  </si>
-  <si>
-    <t>85868</t>
-  </si>
-  <si>
-    <t>4901165202925</t>
-  </si>
-  <si>
-    <t>CUCHILLLA ARTE AK-5 PINK</t>
-  </si>
-  <si>
-    <t>85871</t>
-  </si>
-  <si>
-    <t>CUCHILLLA DE ARTE AK-5/5B</t>
   </si>
   <si>
     <t>85166</t>
@@ -1562,7 +1568,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1580,11 +1586,21 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1594,6 +1610,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF13DAEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1614,7 +1640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1623,6 +1649,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2015,7 +2053,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>6770</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2038,7 +2076,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>27406</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2061,7 +2099,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>7881</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -2084,7 +2122,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>20889</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2107,7 +2145,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>36483</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -2129,11 +2167,11 @@
       <c r="E7">
         <v>120</v>
       </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
+      <c r="F7" s="4">
+        <v>1031</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2141,22 +2179,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="F8" s="4">
+        <v>268</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2164,22 +2202,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="F9" s="4">
+        <v>253</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2187,22 +2225,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="F10" s="4">
+        <v>59</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2210,22 +2248,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2233,22 +2271,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="4">
+        <v>132</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2256,22 +2294,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="F13" s="4">
+        <v>191</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2279,22 +2317,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="4">
+        <v>189</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2302,22 +2340,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="F15" s="4">
+        <v>84</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2325,22 +2363,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E16">
         <v>120</v>
       </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="F16" s="4">
+        <v>692</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2348,22 +2386,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="F17" s="4">
+        <v>257</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2371,22 +2409,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>120</v>
       </c>
-      <c r="F18" s="2">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+      <c r="F18" s="4">
+        <v>983</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2394,22 +2432,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="F19" s="4">
+        <v>195</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2417,22 +2455,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="F20" s="4">
+        <v>75</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2440,22 +2478,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="F21" s="4">
+        <v>439</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2463,19 +2501,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E22">
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>2053</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2486,22 +2524,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="F23" s="4">
+        <v>3</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2509,22 +2547,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="F24" s="4">
+        <v>113</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2532,22 +2570,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="F25" s="4">
+        <v>348</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2555,22 +2593,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="F26" s="4">
+        <v>123</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2578,22 +2616,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="F27" s="4">
+        <v>160</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2601,19 +2639,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E28">
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>9252</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2624,22 +2662,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="F29" s="4">
+        <v>94</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2647,22 +2685,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="F30" s="4">
+        <v>56</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2670,19 +2708,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E31">
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>3120</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -2693,19 +2731,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E32">
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>1445</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2716,22 +2754,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="6">
         <v>0</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="G33" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2739,22 +2777,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E34">
         <v>120</v>
       </c>
-      <c r="F34" s="2">
-        <v>0</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>10</v>
+      <c r="F34" s="4">
+        <v>907</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2762,22 +2800,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="6">
         <v>0</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2785,22 +2823,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="2">
-        <v>0</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="F36" s="4">
+        <v>118</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2808,22 +2846,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="2">
-        <v>0</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="F37" s="4">
+        <v>944</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2831,22 +2869,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="2">
-        <v>0</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="F38" s="4">
+        <v>123</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2854,22 +2892,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="2">
-        <v>0</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="F39" s="4">
+        <v>278</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2877,22 +2915,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="F40" s="4">
+        <v>245</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2900,22 +2938,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="2">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="F41" s="4">
+        <v>107</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2923,22 +2961,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="F42" s="4">
+        <v>273</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2946,19 +2984,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E43">
         <v>240</v>
       </c>
       <c r="F43" s="2">
-        <v>0</v>
+        <v>2865</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -2969,22 +3007,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="F44" s="4">
+        <v>1090</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2992,22 +3030,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="F45" s="4">
+        <v>163</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3015,22 +3053,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="2">
-        <v>0</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>10</v>
+      <c r="F46" s="4">
+        <v>1475</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3038,22 +3076,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="2">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="F47" s="4">
+        <v>164</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3061,22 +3099,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="2">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="F48" s="4">
+        <v>140</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3084,22 +3122,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D49" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="2">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+      <c r="F49" s="4">
+        <v>261</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3107,22 +3145,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="F50" s="4">
+        <v>291</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3130,22 +3168,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D51" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="2">
-        <v>0</v>
-      </c>
-      <c r="G51" s="3" t="s">
+      <c r="F51" s="4">
         <v>10</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3153,22 +3191,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D52" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="F52" s="4">
+        <v>82</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3176,22 +3214,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="2">
-        <v>0</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="F53" s="4">
+        <v>27</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3199,22 +3237,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C54" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D54" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="F54" s="4">
+        <v>2462</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3222,22 +3260,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="2">
-        <v>0</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="F55" s="4">
+        <v>208</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3245,22 +3283,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C56" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D56" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="6">
         <v>0</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="G56" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3268,22 +3306,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E57">
         <v>720</v>
       </c>
-      <c r="F57" s="2">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="F57" s="4">
+        <v>4873</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3291,22 +3329,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C58" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D58" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="F58" s="4">
+        <v>201</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3314,22 +3352,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C59" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D59" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="6">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>10</v>
+      <c r="G59" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3337,22 +3375,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="6">
         <v>0</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="G60" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3360,22 +3398,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D61" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>10</v>
+      <c r="F61" s="4">
+        <v>300</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3383,22 +3421,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="2">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>198</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3406,19 +3444,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C63" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D63" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E63">
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>7884</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3429,22 +3467,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E64">
         <v>60</v>
       </c>
-      <c r="F64" s="2">
-        <v>0</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>10</v>
+      <c r="F64" s="4">
+        <v>513</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3452,22 +3490,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C65" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="2">
-        <v>0</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="F65" s="4">
+        <v>65</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3475,22 +3513,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C66" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D66" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="2">
-        <v>0</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="4">
+        <v>69</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3498,22 +3536,22 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C67" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D67" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="6">
         <v>0</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="G67" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3521,22 +3559,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C68" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D68" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="2">
-        <v>0</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="F68" s="4">
+        <v>55</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3544,19 +3582,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C69" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D69" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E69">
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>0</v>
+        <v>4170</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3567,22 +3605,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D70" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="2">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="F70" s="4">
+        <v>130</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3590,22 +3628,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C71" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D71" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="6">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="G71" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3613,22 +3651,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C72" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D72" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="2">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+      <c r="F72" s="4">
+        <v>412</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3636,22 +3674,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C73" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D73" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="2">
-        <v>0</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="F73" s="4">
+        <v>500</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3659,22 +3697,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C74" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D74" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="2">
-        <v>0</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="F74" s="4">
+        <v>1529</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3682,19 +3720,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C75" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D75" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E75">
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>0</v>
+        <v>4001</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3705,22 +3743,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C76" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="6">
         <v>0</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="G76" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3728,22 +3766,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D77" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="2">
-        <v>0</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="F77" s="4">
+        <v>539</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3751,22 +3789,22 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C78" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D78" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="2">
-        <v>0</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="F78" s="4">
+        <v>114</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3774,22 +3812,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D79" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="2">
-        <v>0</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="F79" s="4">
+        <v>4</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3797,22 +3835,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C80" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D80" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="2">
-        <v>0</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>10</v>
+      <c r="F80" s="4">
+        <v>12</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3820,19 +3858,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C81" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D81" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E81">
         <v>20</v>
       </c>
       <c r="F81" s="2">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -3843,19 +3881,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C82" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D82" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E82">
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>0</v>
+        <v>2766</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -3866,22 +3904,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C83" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D83" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="6">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="G83" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3889,22 +3927,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C84" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D84" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E84">
         <v>40</v>
       </c>
-      <c r="F84" s="2">
-        <v>0</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>10</v>
+      <c r="F84" s="4">
+        <v>80</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3912,22 +3950,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C85" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D85" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="6">
         <v>0</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>10</v>
+      <c r="G85" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3935,22 +3973,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D86" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="6">
         <v>0</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="G86" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -3958,22 +3996,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C87" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D87" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="6">
         <v>0</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="G87" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -3981,22 +4019,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="6">
         <v>0</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>10</v>
+      <c r="G88" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4004,19 +4042,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C89" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D89" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E89">
         <v>20</v>
       </c>
       <c r="F89" s="2">
-        <v>0</v>
+        <v>1473</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -4027,19 +4065,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C90" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D90" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E90">
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>0</v>
+        <v>108017</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4050,22 +4088,22 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C91" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D91" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E91">
         <v>10</v>
       </c>
-      <c r="F91" s="2">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>10</v>
+      <c r="F91" s="4">
+        <v>68</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4073,19 +4111,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C92" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D92" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E92">
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4096,19 +4134,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C93" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D93" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4119,19 +4157,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E94">
         <v>6</v>
       </c>
       <c r="F94" s="2">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4142,22 +4180,22 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D95" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="6">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>10</v>
+      <c r="G95" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4165,22 +4203,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D96" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="6">
         <v>0</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="G96" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4188,22 +4226,22 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C97" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D97" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="2">
-        <v>0</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>10</v>
+      <c r="F97" s="4">
+        <v>7</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4211,22 +4249,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C98" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D98" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="6">
         <v>0</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="G98" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4234,22 +4272,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C99" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D99" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E99">
         <v>5</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="6">
         <v>0</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>10</v>
+      <c r="G99" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4257,19 +4295,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C100" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D100" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E100">
         <v>6</v>
       </c>
       <c r="F100" s="2">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4280,19 +4318,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C101" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D101" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E101">
         <v>6</v>
       </c>
       <c r="F101" s="2">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4303,19 +4341,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C102" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D102" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E102">
         <v>6</v>
       </c>
       <c r="F102" s="2">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4326,19 +4364,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C103" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D103" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E103">
         <v>6</v>
       </c>
       <c r="F103" s="2">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>10</v>
@@ -4349,22 +4387,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C104" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D104" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="2">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>10</v>
+      <c r="F104" s="4">
+        <v>4</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4372,22 +4410,22 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C105" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D105" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E105">
         <v>56</v>
       </c>
-      <c r="F105" s="2">
-        <v>0</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>10</v>
+      <c r="F105" s="4">
+        <v>354</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4395,22 +4433,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C106" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D106" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="2">
-        <v>0</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="F106" s="4">
+        <v>15</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4418,22 +4456,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C107" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D107" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="2">
-        <v>0</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>10</v>
+      <c r="F107" s="4">
+        <v>1</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4441,22 +4479,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C108" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D108" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="2">
-        <v>0</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="F108" s="4">
+        <v>79</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4464,22 +4502,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C109" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D109" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="6">
         <v>0</v>
       </c>
-      <c r="G109" s="3" t="s">
-        <v>10</v>
+      <c r="G109" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4487,19 +4525,19 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C110" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D110" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E110">
         <v>54</v>
       </c>
       <c r="F110" s="2">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4510,22 +4548,22 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C111" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D111" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="6">
         <v>0</v>
       </c>
-      <c r="G111" s="3" t="s">
-        <v>10</v>
+      <c r="G111" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4533,22 +4571,22 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C112" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D112" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="6">
         <v>0</v>
       </c>
-      <c r="G112" s="3" t="s">
-        <v>10</v>
+      <c r="G112" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4556,22 +4594,22 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C113" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D113" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="6">
         <v>0</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>10</v>
+      <c r="G113" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4579,22 +4617,22 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C114" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D114" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E114">
         <v>5</v>
       </c>
-      <c r="F114" s="2">
-        <v>0</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>10</v>
+      <c r="F114" s="4">
+        <v>39</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -4602,22 +4640,22 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C115" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D115" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="2">
-        <v>0</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="F115" s="4">
+        <v>312</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4625,22 +4663,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C116" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D116" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="6">
         <v>0</v>
       </c>
-      <c r="G116" s="3" t="s">
-        <v>10</v>
+      <c r="G116" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4648,22 +4686,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C117" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D117" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="2">
-        <v>0</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="F117" s="4">
+        <v>2</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4671,19 +4709,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C118" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D118" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E118">
         <v>10</v>
       </c>
       <c r="F118" s="2">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -4694,22 +4732,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C119" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D119" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="2">
-        <v>0</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>10</v>
+      <c r="F119" s="4">
+        <v>6</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4717,22 +4755,22 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C120" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D120" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="2">
-        <v>0</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="F120" s="4">
+        <v>36</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4740,22 +4778,22 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C121" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D121" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="6">
         <v>0</v>
       </c>
-      <c r="G121" s="3" t="s">
-        <v>10</v>
+      <c r="G121" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4763,22 +4801,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C122" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D122" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="6">
         <v>0</v>
       </c>
-      <c r="G122" s="3" t="s">
-        <v>10</v>
+      <c r="G122" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4786,22 +4824,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C123" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D123" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="2">
-        <v>0</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>10</v>
+      <c r="F123" s="4">
+        <v>127</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4809,22 +4847,22 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C124" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D124" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E124">
         <v>4</v>
       </c>
-      <c r="F124" s="2">
-        <v>0</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>10</v>
+      <c r="F124" s="4">
+        <v>37</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -4832,22 +4870,22 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C125" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D125" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="6">
         <v>0</v>
       </c>
-      <c r="G125" s="3" t="s">
-        <v>10</v>
+      <c r="G125" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4855,22 +4893,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C126" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D126" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="2">
-        <v>0</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="F126" s="4">
+        <v>17</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4878,22 +4916,22 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C127" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D127" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E127">
         <v>4</v>
       </c>
-      <c r="F127" s="2">
-        <v>0</v>
-      </c>
-      <c r="G127" s="3" t="s">
-        <v>10</v>
+      <c r="F127" s="4">
+        <v>24</v>
+      </c>
+      <c r="G127" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -4901,22 +4939,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C128" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D128" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="2">
-        <v>0</v>
-      </c>
-      <c r="G128" s="3" t="s">
-        <v>10</v>
+      <c r="F128" s="4">
+        <v>18</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4924,22 +4962,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C129" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D129" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="2">
-        <v>0</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>10</v>
+      <c r="F129" s="4">
+        <v>4</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4947,22 +4985,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C130" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D130" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="2">
-        <v>0</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="F130" s="4">
+        <v>3</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -4970,22 +5008,22 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C131" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D131" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E131">
         <v>60</v>
       </c>
-      <c r="F131" s="2">
-        <v>0</v>
-      </c>
-      <c r="G131" s="3" t="s">
-        <v>10</v>
+      <c r="F131" s="4">
+        <v>357</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -4993,22 +5031,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C132" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D132" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="2">
-        <v>0</v>
-      </c>
-      <c r="G132" s="3" t="s">
-        <v>10</v>
+      <c r="F132" s="4">
+        <v>58</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5016,22 +5054,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C133" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D133" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="2">
-        <v>0</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="F133" s="4">
+        <v>138</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5039,22 +5077,22 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C134" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D134" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E134">
         <v>60</v>
       </c>
-      <c r="F134" s="2">
-        <v>0</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>10</v>
+      <c r="F134" s="4">
+        <v>480</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5062,22 +5100,22 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C135" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D135" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E135">
         <v>60</v>
       </c>
-      <c r="F135" s="2">
-        <v>0</v>
-      </c>
-      <c r="G135" s="3" t="s">
-        <v>10</v>
+      <c r="F135" s="4">
+        <v>521</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5085,22 +5123,22 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C136" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D136" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E136">
         <v>60</v>
       </c>
-      <c r="F136" s="2">
-        <v>0</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>10</v>
+      <c r="F136" s="4">
+        <v>480</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5108,19 +5146,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C137" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E137">
         <v>30</v>
       </c>
       <c r="F137" s="2">
-        <v>0</v>
+        <v>1601</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>10</v>
@@ -5131,19 +5169,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C138" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D138" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E138">
         <v>40</v>
       </c>
       <c r="F138" s="2">
-        <v>0</v>
+        <v>1130</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>10</v>
@@ -5154,22 +5192,22 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C139" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E139">
         <v>63</v>
       </c>
-      <c r="F139" s="2">
-        <v>0</v>
-      </c>
-      <c r="G139" s="3" t="s">
-        <v>10</v>
+      <c r="F139" s="4">
+        <v>566</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5177,19 +5215,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C140" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E140">
         <v>10</v>
       </c>
       <c r="F140" s="2">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>10</v>
@@ -5200,22 +5238,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C141" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="2">
-        <v>0</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="F141" s="4">
+        <v>108</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5223,22 +5261,22 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C142" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="2">
-        <v>0</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="F142" s="4">
+        <v>122</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5246,22 +5284,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C143" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="2">
-        <v>0</v>
-      </c>
-      <c r="G143" s="3" t="s">
-        <v>10</v>
+      <c r="F143" s="4">
+        <v>15</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5269,22 +5307,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C144" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="6">
         <v>0</v>
       </c>
-      <c r="G144" s="3" t="s">
-        <v>10</v>
+      <c r="G144" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5292,22 +5330,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C145" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D145" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="2">
-        <v>0</v>
-      </c>
-      <c r="G145" s="3" t="s">
+      <c r="F145" s="4">
         <v>10</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5315,22 +5353,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D146" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="2">
-        <v>0</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="F146" s="4">
+        <v>34</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5338,22 +5376,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C147" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D147" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="6">
         <v>0</v>
       </c>
-      <c r="G147" s="3" t="s">
-        <v>10</v>
+      <c r="G147" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5361,22 +5399,22 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C148" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D148" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E148">
         <v>5</v>
       </c>
-      <c r="F148" s="2">
-        <v>0</v>
-      </c>
-      <c r="G148" s="3" t="s">
-        <v>10</v>
+      <c r="F148" s="4">
+        <v>30</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -5384,19 +5422,19 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C149" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D149" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E149">
         <v>5</v>
       </c>
       <c r="F149" s="2">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>10</v>
@@ -5407,19 +5445,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C150" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D150" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E150">
         <v>5</v>
       </c>
       <c r="F150" s="2">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -5430,19 +5468,19 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C151" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D151" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151" s="2">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5453,22 +5491,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C152" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D152" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="2">
-        <v>0</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>10</v>
+      <c r="F152" s="4">
+        <v>8</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5476,22 +5514,22 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C153" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D153" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="2">
-        <v>0</v>
-      </c>
-      <c r="G153" s="3" t="s">
-        <v>10</v>
+      <c r="F153" s="4">
+        <v>640</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5499,22 +5537,22 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C154" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="2">
-        <v>0</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>10</v>
+      <c r="F154" s="4">
+        <v>121</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5522,19 +5560,19 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C155" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E155">
         <v>60</v>
       </c>
       <c r="F155" s="2">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>10</v>
@@ -5545,22 +5583,22 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C156" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="6">
         <v>0</v>
       </c>
-      <c r="G156" s="3" t="s">
-        <v>10</v>
+      <c r="G156" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5568,22 +5606,22 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C157" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D157" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="2">
-        <v>0</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>10</v>
+      <c r="F157" s="4">
+        <v>66</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5591,22 +5629,22 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C158" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D158" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="2">
-        <v>0</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="F158" s="4">
+        <v>30</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5614,22 +5652,22 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="2">
-        <v>0</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="F159" s="4">
+        <v>83</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5637,22 +5675,22 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C160" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D160" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="2">
-        <v>0</v>
-      </c>
-      <c r="G160" s="3" t="s">
+      <c r="F160" s="4">
         <v>10</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5660,22 +5698,22 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C161" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D161" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="2">
-        <v>0</v>
-      </c>
-      <c r="G161" s="3" t="s">
-        <v>10</v>
+      <c r="F161" s="4">
+        <v>51</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5683,22 +5721,22 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C162" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D162" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="2">
-        <v>0</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>10</v>
+      <c r="F162" s="4">
+        <v>74</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5706,22 +5744,22 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C163" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D163" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="2">
-        <v>0</v>
-      </c>
-      <c r="G163" s="3" t="s">
-        <v>10</v>
+      <c r="F163" s="4">
+        <v>11</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5729,22 +5767,22 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C164" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D164" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="2">
-        <v>0</v>
-      </c>
-      <c r="G164" s="3" t="s">
-        <v>10</v>
+      <c r="F164" s="4">
+        <v>4</v>
+      </c>
+      <c r="G164" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5752,22 +5790,22 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C165" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D165" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="2">
-        <v>0</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>10</v>
+      <c r="F165" s="4">
+        <v>35</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5775,22 +5813,22 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C166" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D166" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="2">
-        <v>0</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>10</v>
+      <c r="F166" s="4">
+        <v>62</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5798,22 +5836,22 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C167" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D167" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="2">
-        <v>0</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>10</v>
+      <c r="F167" s="4">
+        <v>28</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5821,22 +5859,22 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C168" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D168" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="2">
-        <v>0</v>
-      </c>
-      <c r="G168" s="3" t="s">
-        <v>10</v>
+      <c r="F168" s="4">
+        <v>920</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5844,22 +5882,22 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C169" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D169" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="2">
-        <v>0</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>10</v>
+      <c r="F169" s="4">
+        <v>102</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5867,22 +5905,22 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C170" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D170" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="2">
-        <v>0</v>
-      </c>
-      <c r="G170" s="3" t="s">
-        <v>10</v>
+      <c r="F170" s="4">
+        <v>211</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5890,22 +5928,22 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C171" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D171" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="2">
-        <v>0</v>
-      </c>
-      <c r="G171" s="3" t="s">
-        <v>10</v>
+      <c r="F171" s="4">
+        <v>753</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -5913,22 +5951,22 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C172" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D172" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="2">
-        <v>0</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>10</v>
+      <c r="F172" s="4">
+        <v>31</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5936,22 +5974,22 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C173" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D173" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="2">
-        <v>0</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>10</v>
+      <c r="F173" s="4">
+        <v>93</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -5959,22 +5997,22 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C174" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D174" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="2">
-        <v>0</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>10</v>
+      <c r="F174" s="4">
+        <v>378</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -5982,22 +6020,22 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C175" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D175" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="2">
-        <v>0</v>
-      </c>
-      <c r="G175" s="3" t="s">
-        <v>10</v>
+      <c r="F175" s="4">
+        <v>94</v>
+      </c>
+      <c r="G175" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6005,22 +6043,22 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C176" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D176" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="2">
-        <v>0</v>
-      </c>
-      <c r="G176" s="3" t="s">
-        <v>10</v>
+      <c r="F176" s="4">
+        <v>103</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6028,22 +6066,22 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C177" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D177" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="2">
-        <v>0</v>
-      </c>
-      <c r="G177" s="3" t="s">
-        <v>10</v>
+      <c r="F177" s="4">
+        <v>93</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6051,22 +6089,22 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C178" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D178" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="2">
-        <v>0</v>
-      </c>
-      <c r="G178" s="3" t="s">
-        <v>10</v>
+      <c r="F178" s="4">
+        <v>68</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6074,22 +6112,22 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C179" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D179" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E179">
         <v>12</v>
       </c>
-      <c r="F179" s="2">
-        <v>0</v>
-      </c>
-      <c r="G179" s="3" t="s">
-        <v>10</v>
+      <c r="F179" s="4">
+        <v>77</v>
+      </c>
+      <c r="G179" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6097,22 +6135,22 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C180" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D180" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="6">
         <v>0</v>
       </c>
-      <c r="G180" s="3" t="s">
-        <v>10</v>
+      <c r="G180" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6120,22 +6158,22 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C181" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D181" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="2">
-        <v>0</v>
-      </c>
-      <c r="G181" s="3" t="s">
-        <v>10</v>
+      <c r="F181" s="4">
+        <v>4</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6143,22 +6181,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C182" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D182" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="2">
-        <v>0</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>10</v>
+      <c r="F182" s="4">
+        <v>6</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6166,19 +6204,19 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C183" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D183" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E183">
         <v>1</v>
       </c>
       <c r="F183" s="2">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>10</v>
@@ -6189,19 +6227,19 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C184" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D184" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E184">
         <v>20</v>
       </c>
       <c r="F184" s="2">
-        <v>0</v>
+        <v>3763</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>10</v>
@@ -6212,22 +6250,22 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C185" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D185" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E185">
         <v>20</v>
       </c>
-      <c r="F185" s="2">
-        <v>0</v>
-      </c>
-      <c r="G185" s="3" t="s">
-        <v>10</v>
+      <c r="F185" s="4">
+        <v>144</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -6235,22 +6273,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C186" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D186" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="2">
-        <v>0</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>10</v>
+      <c r="F186" s="4">
+        <v>40</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6258,22 +6296,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C187" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D187" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="2">
-        <v>0</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="F187" s="4">
+        <v>20</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6281,22 +6319,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C188" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D188" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="2">
-        <v>0</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>10</v>
+      <c r="F188" s="4">
+        <v>17</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6304,22 +6342,22 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C189" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D189" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E189">
         <v>50</v>
       </c>
-      <c r="F189" s="2">
-        <v>0</v>
-      </c>
-      <c r="G189" s="3" t="s">
-        <v>10</v>
+      <c r="F189" s="4">
+        <v>380</v>
+      </c>
+      <c r="G189" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6327,19 +6365,19 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C190" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D190" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E190">
         <v>50</v>
       </c>
       <c r="F190" s="2">
-        <v>0</v>
+        <v>1181</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -6350,19 +6388,19 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C191" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D191" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E191">
         <v>50</v>
       </c>
       <c r="F191" s="2">
-        <v>0</v>
+        <v>1873</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6373,19 +6411,19 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C192" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D192" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E192">
         <v>50</v>
       </c>
       <c r="F192" s="2">
-        <v>0</v>
+        <v>1210</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6396,19 +6434,19 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C193" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D193" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E193">
         <v>50</v>
       </c>
       <c r="F193" s="2">
-        <v>0</v>
+        <v>19771</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6419,19 +6457,19 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C194" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D194" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E194">
         <v>100</v>
       </c>
       <c r="F194" s="2">
-        <v>0</v>
+        <v>1181</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
@@ -6442,22 +6480,22 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C195" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D195" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E195">
         <v>60</v>
       </c>
-      <c r="F195" s="2">
-        <v>0</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>10</v>
+      <c r="F195" s="4">
+        <v>454</v>
+      </c>
+      <c r="G195" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6465,22 +6503,22 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C196" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D196" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E196">
         <v>100</v>
       </c>
-      <c r="F196" s="2">
-        <v>0</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>10</v>
+      <c r="F196" s="4">
+        <v>880</v>
+      </c>
+      <c r="G196" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6488,19 +6526,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C197" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D197" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E197">
         <v>80</v>
       </c>
       <c r="F197" s="2">
-        <v>0</v>
+        <v>1247</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
@@ -1578,6 +1578,7 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>

--- a/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="517">
   <si>
     <t>#</t>
   </si>
@@ -43,85 +43,91 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
+    <t>✓ OK</t>
+  </si>
+  <si>
+    <t>85007</t>
+  </si>
+  <si>
+    <t>7754807850063</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85768</t>
+  </si>
+  <si>
+    <t>7754807857680</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85008</t>
+  </si>
+  <si>
+    <t>7754807850087</t>
+  </si>
+  <si>
+    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85801</t>
+  </si>
+  <si>
+    <t>7754807857024</t>
+  </si>
+  <si>
+    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
+  </si>
+  <si>
+    <t>85163</t>
+  </si>
+  <si>
+    <t>091511400595</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-1/5B</t>
+  </si>
+  <si>
+    <t>85164</t>
+  </si>
+  <si>
+    <t>091511400670</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-4</t>
+  </si>
+  <si>
+    <t>⚠ BAJO</t>
+  </si>
+  <si>
+    <t>85770</t>
+  </si>
+  <si>
+    <t>091511220292</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-5 + KB-5/30B</t>
+  </si>
+  <si>
+    <t>85868</t>
+  </si>
+  <si>
+    <t>4901165202925</t>
+  </si>
+  <si>
+    <t>CUCHILLLA ARTE AK-5 PINK</t>
+  </si>
+  <si>
+    <t>85871</t>
+  </si>
+  <si>
+    <t>CUCHILLLA DE ARTE AK-5/5B</t>
+  </si>
+  <si>
     <t>✗ AGOTADO</t>
-  </si>
-  <si>
-    <t>85007</t>
-  </si>
-  <si>
-    <t>7754807850063</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85768</t>
-  </si>
-  <si>
-    <t>7754807857680</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85008</t>
-  </si>
-  <si>
-    <t>7754807850087</t>
-  </si>
-  <si>
-    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85801</t>
-  </si>
-  <si>
-    <t>7754807857024</t>
-  </si>
-  <si>
-    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
-  </si>
-  <si>
-    <t>85163</t>
-  </si>
-  <si>
-    <t>091511400595</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-1/5B</t>
-  </si>
-  <si>
-    <t>85164</t>
-  </si>
-  <si>
-    <t>091511400670</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-4</t>
-  </si>
-  <si>
-    <t>85770</t>
-  </si>
-  <si>
-    <t>091511220292</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-5 + KB-5/30B</t>
-  </si>
-  <si>
-    <t>85868</t>
-  </si>
-  <si>
-    <t>4901165202925</t>
-  </si>
-  <si>
-    <t>CUCHILLLA ARTE AK-5 PINK</t>
-  </si>
-  <si>
-    <t>85871</t>
-  </si>
-  <si>
-    <t>CUCHILLLA DE ARTE AK-5/5B</t>
   </si>
   <si>
     <t>85166</t>
@@ -1562,7 +1568,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1581,11 +1587,21 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1595,6 +1611,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF13DAEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1615,7 +1641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1624,6 +1650,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2016,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>6770</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2039,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>27406</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2062,7 +2100,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>7881</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -2085,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>20889</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2108,7 +2146,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>36483</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -2131,7 +2169,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -2153,11 +2191,11 @@
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="F8" s="4">
+        <v>268</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2165,22 +2203,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="F9" s="4">
+        <v>253</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2188,22 +2226,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="F10" s="4">
+        <v>59</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2211,22 +2249,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2234,22 +2272,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="4">
+        <v>132</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2257,22 +2295,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="F13" s="4">
+        <v>191</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2280,22 +2318,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="4">
+        <v>189</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2303,22 +2341,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="F15" s="4">
+        <v>84</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2326,19 +2364,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E16">
         <v>120</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -2349,22 +2387,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="F17" s="4">
+        <v>257</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2372,19 +2410,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>120</v>
       </c>
       <c r="F18" s="2">
-        <v>0</v>
+        <v>983</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -2395,22 +2433,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="F19" s="4">
+        <v>195</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2418,22 +2456,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="F20" s="4">
+        <v>75</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2441,22 +2479,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="F21" s="4">
+        <v>439</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2464,19 +2502,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E22">
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>2053</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2487,22 +2525,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="F23" s="4">
+        <v>3</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2510,22 +2548,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="F24" s="4">
+        <v>113</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2533,22 +2571,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="F25" s="4">
+        <v>348</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2556,22 +2594,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="F26" s="4">
+        <v>123</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2579,22 +2617,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="F27" s="4">
+        <v>160</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,19 +2640,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E28">
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>9252</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2625,22 +2663,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="F29" s="4">
+        <v>94</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2648,22 +2686,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="F30" s="4">
+        <v>56</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2671,19 +2709,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E31">
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>3120</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -2694,19 +2732,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E32">
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>1445</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2717,22 +2755,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="6">
         <v>0</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="G33" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2740,19 +2778,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E34">
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -2763,22 +2801,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="6">
         <v>0</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2786,22 +2824,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="2">
-        <v>0</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="F36" s="4">
+        <v>118</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2809,22 +2847,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="2">
-        <v>0</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="F37" s="4">
+        <v>944</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2832,22 +2870,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="2">
-        <v>0</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="F38" s="4">
+        <v>123</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2855,22 +2893,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="2">
-        <v>0</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="F39" s="4">
+        <v>278</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2878,22 +2916,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="F40" s="4">
+        <v>245</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2901,22 +2939,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="2">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="F41" s="4">
+        <v>107</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2924,22 +2962,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="F42" s="4">
+        <v>273</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2947,19 +2985,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E43">
         <v>240</v>
       </c>
       <c r="F43" s="2">
-        <v>0</v>
+        <v>2865</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -2970,22 +3008,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="F44" s="4">
+        <v>1090</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2993,22 +3031,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="F45" s="4">
+        <v>163</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3016,22 +3054,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="2">
-        <v>0</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>10</v>
+      <c r="F46" s="4">
+        <v>1475</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3039,22 +3077,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="2">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="F47" s="4">
+        <v>164</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3062,22 +3100,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="2">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="F48" s="4">
+        <v>140</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3085,22 +3123,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D49" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="2">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+      <c r="F49" s="4">
+        <v>261</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3108,22 +3146,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="F50" s="4">
+        <v>291</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3131,22 +3169,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D51" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="2">
-        <v>0</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>10</v>
+      <c r="F51" s="4">
+        <v>10</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3154,22 +3192,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D52" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="F52" s="4">
+        <v>82</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3177,22 +3215,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="2">
-        <v>0</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="F53" s="4">
+        <v>27</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3200,22 +3238,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C54" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D54" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="F54" s="4">
+        <v>2462</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3223,22 +3261,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="2">
-        <v>0</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="F55" s="4">
+        <v>208</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3246,22 +3284,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C56" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D56" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="6">
         <v>0</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="G56" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3269,19 +3307,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E57">
         <v>720</v>
       </c>
       <c r="F57" s="2">
-        <v>0</v>
+        <v>4873</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3292,22 +3330,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C58" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D58" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="F58" s="4">
+        <v>201</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3315,22 +3353,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C59" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D59" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="6">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>10</v>
+      <c r="G59" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3338,22 +3376,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="6">
         <v>0</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="G60" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3361,22 +3399,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D61" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>10</v>
+      <c r="F61" s="4">
+        <v>300</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3384,22 +3422,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="2">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>198</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3407,19 +3445,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C63" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D63" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E63">
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>7884</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3430,19 +3468,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E64">
         <v>60</v>
       </c>
       <c r="F64" s="2">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -3453,22 +3491,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C65" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="2">
-        <v>0</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="F65" s="4">
+        <v>65</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3476,22 +3514,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C66" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D66" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="2">
-        <v>0</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="4">
+        <v>69</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3499,22 +3537,22 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C67" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D67" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="6">
         <v>0</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="G67" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3522,22 +3560,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C68" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D68" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="2">
-        <v>0</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="F68" s="4">
+        <v>55</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3545,19 +3583,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C69" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D69" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E69">
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>0</v>
+        <v>4170</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3568,22 +3606,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D70" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="2">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="F70" s="4">
+        <v>130</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3591,22 +3629,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C71" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D71" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="6">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="G71" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3614,22 +3652,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C72" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D72" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="2">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+      <c r="F72" s="4">
+        <v>412</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3637,22 +3675,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C73" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D73" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="2">
-        <v>0</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="F73" s="4">
+        <v>500</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3660,19 +3698,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C74" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D74" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E74">
         <v>240</v>
       </c>
       <c r="F74" s="2">
-        <v>0</v>
+        <v>1529</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3683,19 +3721,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C75" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D75" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E75">
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>0</v>
+        <v>4001</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3706,22 +3744,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C76" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="6">
         <v>0</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="G76" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3729,22 +3767,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D77" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="2">
-        <v>0</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="F77" s="4">
+        <v>539</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3752,22 +3790,22 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C78" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D78" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="2">
-        <v>0</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="F78" s="4">
+        <v>114</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3775,22 +3813,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D79" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="2">
-        <v>0</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="F79" s="4">
+        <v>4</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3798,22 +3836,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C80" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D80" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="2">
-        <v>0</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>10</v>
+      <c r="F80" s="4">
+        <v>12</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3821,19 +3859,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C81" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D81" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E81">
         <v>20</v>
       </c>
       <c r="F81" s="2">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -3844,19 +3882,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C82" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D82" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E82">
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>0</v>
+        <v>2766</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -3867,22 +3905,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C83" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D83" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="6">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="G83" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3890,22 +3928,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C84" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D84" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E84">
         <v>40</v>
       </c>
-      <c r="F84" s="2">
-        <v>0</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>10</v>
+      <c r="F84" s="4">
+        <v>80</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3913,22 +3951,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C85" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D85" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="6">
         <v>0</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>10</v>
+      <c r="G85" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3936,22 +3974,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D86" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="6">
         <v>0</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="G86" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -3959,22 +3997,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C87" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D87" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="6">
         <v>0</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="G87" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -3982,22 +4020,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="6">
         <v>0</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>10</v>
+      <c r="G88" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4005,19 +4043,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C89" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D89" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E89">
         <v>20</v>
       </c>
       <c r="F89" s="2">
-        <v>0</v>
+        <v>1473</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -4028,19 +4066,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C90" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D90" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E90">
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>0</v>
+        <v>108017</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4051,19 +4089,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C91" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D91" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E91">
         <v>10</v>
       </c>
       <c r="F91" s="2">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4074,19 +4112,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C92" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D92" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E92">
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4097,19 +4135,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C93" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D93" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4120,19 +4158,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E94">
         <v>6</v>
       </c>
       <c r="F94" s="2">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4143,22 +4181,22 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D95" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="6">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>10</v>
+      <c r="G95" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4166,22 +4204,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D96" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="6">
         <v>0</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="G96" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4189,22 +4227,22 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C97" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D97" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="2">
-        <v>0</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>10</v>
+      <c r="F97" s="4">
+        <v>7</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4212,22 +4250,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C98" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D98" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="6">
         <v>0</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="G98" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4235,22 +4273,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C99" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D99" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E99">
         <v>5</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="6">
         <v>0</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>10</v>
+      <c r="G99" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4258,19 +4296,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C100" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D100" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E100">
         <v>6</v>
       </c>
       <c r="F100" s="2">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4281,19 +4319,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C101" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D101" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E101">
         <v>6</v>
       </c>
       <c r="F101" s="2">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4304,19 +4342,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C102" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D102" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E102">
         <v>6</v>
       </c>
       <c r="F102" s="2">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4327,19 +4365,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C103" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D103" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E103">
         <v>6</v>
       </c>
       <c r="F103" s="2">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>10</v>
@@ -4350,22 +4388,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C104" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D104" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="2">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>10</v>
+      <c r="F104" s="4">
+        <v>4</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4373,19 +4411,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C105" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D105" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E105">
         <v>56</v>
       </c>
       <c r="F105" s="2">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>10</v>
@@ -4396,22 +4434,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C106" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D106" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="2">
-        <v>0</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="F106" s="4">
+        <v>15</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4419,22 +4457,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C107" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D107" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="2">
-        <v>0</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>10</v>
+      <c r="F107" s="4">
+        <v>1</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4442,22 +4480,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C108" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D108" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="2">
-        <v>0</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="F108" s="4">
+        <v>79</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4465,22 +4503,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C109" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D109" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="6">
         <v>0</v>
       </c>
-      <c r="G109" s="3" t="s">
-        <v>10</v>
+      <c r="G109" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4488,19 +4526,19 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C110" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D110" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E110">
         <v>54</v>
       </c>
       <c r="F110" s="2">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4511,22 +4549,22 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C111" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D111" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="6">
         <v>0</v>
       </c>
-      <c r="G111" s="3" t="s">
-        <v>10</v>
+      <c r="G111" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4534,22 +4572,22 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C112" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D112" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="6">
         <v>0</v>
       </c>
-      <c r="G112" s="3" t="s">
-        <v>10</v>
+      <c r="G112" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4557,22 +4595,22 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C113" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D113" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="6">
         <v>0</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>10</v>
+      <c r="G113" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4580,19 +4618,19 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C114" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D114" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E114">
         <v>5</v>
       </c>
       <c r="F114" s="2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4603,22 +4641,22 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C115" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D115" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="2">
-        <v>0</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="F115" s="4">
+        <v>312</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4626,22 +4664,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C116" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D116" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="6">
         <v>0</v>
       </c>
-      <c r="G116" s="3" t="s">
-        <v>10</v>
+      <c r="G116" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4649,22 +4687,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C117" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D117" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="2">
-        <v>0</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="F117" s="4">
+        <v>2</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4672,19 +4710,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C118" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D118" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E118">
         <v>10</v>
       </c>
       <c r="F118" s="2">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -4695,22 +4733,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C119" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D119" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="2">
-        <v>0</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>10</v>
+      <c r="F119" s="4">
+        <v>6</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4718,22 +4756,22 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C120" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D120" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="2">
-        <v>0</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="F120" s="4">
+        <v>36</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4741,22 +4779,22 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C121" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D121" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="6">
         <v>0</v>
       </c>
-      <c r="G121" s="3" t="s">
-        <v>10</v>
+      <c r="G121" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4764,22 +4802,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C122" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D122" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="6">
         <v>0</v>
       </c>
-      <c r="G122" s="3" t="s">
-        <v>10</v>
+      <c r="G122" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4787,22 +4825,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C123" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D123" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="2">
-        <v>0</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>10</v>
+      <c r="F123" s="4">
+        <v>127</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4810,19 +4848,19 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C124" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D124" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E124">
         <v>4</v>
       </c>
       <c r="F124" s="2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -4833,22 +4871,22 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C125" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D125" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="6">
         <v>0</v>
       </c>
-      <c r="G125" s="3" t="s">
-        <v>10</v>
+      <c r="G125" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4856,22 +4894,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C126" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D126" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="2">
-        <v>0</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="F126" s="4">
+        <v>17</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4879,19 +4917,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C127" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D127" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E127">
         <v>4</v>
       </c>
       <c r="F127" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>10</v>
@@ -4902,22 +4940,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C128" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D128" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="2">
-        <v>0</v>
-      </c>
-      <c r="G128" s="3" t="s">
-        <v>10</v>
+      <c r="F128" s="4">
+        <v>18</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4925,22 +4963,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C129" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D129" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="2">
-        <v>0</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>10</v>
+      <c r="F129" s="4">
+        <v>4</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4948,22 +4986,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C130" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D130" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="2">
-        <v>0</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="F130" s="4">
+        <v>3</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -4971,19 +5009,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C131" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D131" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E131">
         <v>60</v>
       </c>
       <c r="F131" s="2">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -4994,22 +5032,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C132" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D132" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="2">
-        <v>0</v>
-      </c>
-      <c r="G132" s="3" t="s">
-        <v>10</v>
+      <c r="F132" s="4">
+        <v>58</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5017,22 +5055,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C133" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D133" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="2">
-        <v>0</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="F133" s="4">
+        <v>138</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5040,19 +5078,19 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C134" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D134" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E134">
         <v>60</v>
       </c>
       <c r="F134" s="2">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>10</v>
@@ -5063,19 +5101,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C135" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D135" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E135">
         <v>60</v>
       </c>
       <c r="F135" s="2">
-        <v>0</v>
+        <v>521</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>10</v>
@@ -5086,19 +5124,19 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C136" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D136" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E136">
         <v>60</v>
       </c>
       <c r="F136" s="2">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>10</v>
@@ -5109,19 +5147,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C137" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E137">
         <v>30</v>
       </c>
       <c r="F137" s="2">
-        <v>0</v>
+        <v>1601</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>10</v>
@@ -5132,19 +5170,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C138" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D138" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E138">
         <v>40</v>
       </c>
       <c r="F138" s="2">
-        <v>0</v>
+        <v>1130</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>10</v>
@@ -5155,19 +5193,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C139" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E139">
         <v>63</v>
       </c>
       <c r="F139" s="2">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
@@ -5178,19 +5216,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C140" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E140">
         <v>10</v>
       </c>
       <c r="F140" s="2">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>10</v>
@@ -5201,22 +5239,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C141" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="2">
-        <v>0</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="F141" s="4">
+        <v>108</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5224,22 +5262,22 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C142" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="2">
-        <v>0</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="F142" s="4">
+        <v>122</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5247,22 +5285,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C143" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="2">
-        <v>0</v>
-      </c>
-      <c r="G143" s="3" t="s">
-        <v>10</v>
+      <c r="F143" s="4">
+        <v>15</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5270,22 +5308,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C144" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="6">
         <v>0</v>
       </c>
-      <c r="G144" s="3" t="s">
-        <v>10</v>
+      <c r="G144" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5293,22 +5331,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C145" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D145" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="2">
-        <v>0</v>
-      </c>
-      <c r="G145" s="3" t="s">
-        <v>10</v>
+      <c r="F145" s="4">
+        <v>10</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5316,22 +5354,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D146" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="2">
-        <v>0</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="F146" s="4">
+        <v>34</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5339,22 +5377,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C147" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D147" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="6">
         <v>0</v>
       </c>
-      <c r="G147" s="3" t="s">
-        <v>10</v>
+      <c r="G147" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5362,19 +5400,19 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C148" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D148" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E148">
         <v>5</v>
       </c>
       <c r="F148" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>10</v>
@@ -5385,19 +5423,19 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C149" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D149" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E149">
         <v>5</v>
       </c>
       <c r="F149" s="2">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>10</v>
@@ -5408,19 +5446,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C150" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D150" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E150">
         <v>5</v>
       </c>
       <c r="F150" s="2">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -5431,19 +5469,19 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C151" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D151" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151" s="2">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5454,22 +5492,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C152" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D152" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="2">
-        <v>0</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>10</v>
+      <c r="F152" s="4">
+        <v>8</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5477,22 +5515,22 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C153" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D153" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="2">
-        <v>0</v>
-      </c>
-      <c r="G153" s="3" t="s">
-        <v>10</v>
+      <c r="F153" s="4">
+        <v>640</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5500,22 +5538,22 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C154" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="2">
-        <v>0</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>10</v>
+      <c r="F154" s="4">
+        <v>121</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5523,19 +5561,19 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C155" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E155">
         <v>60</v>
       </c>
       <c r="F155" s="2">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>10</v>
@@ -5546,22 +5584,22 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C156" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="6">
         <v>0</v>
       </c>
-      <c r="G156" s="3" t="s">
-        <v>10</v>
+      <c r="G156" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5569,22 +5607,22 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C157" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D157" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="2">
-        <v>0</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>10</v>
+      <c r="F157" s="4">
+        <v>66</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5592,22 +5630,22 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C158" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D158" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="2">
-        <v>0</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="F158" s="4">
+        <v>30</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5615,22 +5653,22 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="2">
-        <v>0</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="F159" s="4">
+        <v>83</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5638,22 +5676,22 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C160" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D160" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="2">
-        <v>0</v>
-      </c>
-      <c r="G160" s="3" t="s">
-        <v>10</v>
+      <c r="F160" s="4">
+        <v>10</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5661,22 +5699,22 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C161" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D161" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="2">
-        <v>0</v>
-      </c>
-      <c r="G161" s="3" t="s">
-        <v>10</v>
+      <c r="F161" s="4">
+        <v>51</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5684,22 +5722,22 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C162" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D162" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="2">
-        <v>0</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>10</v>
+      <c r="F162" s="4">
+        <v>74</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5707,22 +5745,22 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C163" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D163" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="2">
-        <v>0</v>
-      </c>
-      <c r="G163" s="3" t="s">
-        <v>10</v>
+      <c r="F163" s="4">
+        <v>11</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5730,22 +5768,22 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C164" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D164" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="2">
-        <v>0</v>
-      </c>
-      <c r="G164" s="3" t="s">
-        <v>10</v>
+      <c r="F164" s="4">
+        <v>4</v>
+      </c>
+      <c r="G164" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5753,22 +5791,22 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C165" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D165" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="2">
-        <v>0</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>10</v>
+      <c r="F165" s="4">
+        <v>35</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5776,22 +5814,22 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C166" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D166" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="2">
-        <v>0</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>10</v>
+      <c r="F166" s="4">
+        <v>62</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5799,22 +5837,22 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C167" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D167" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="2">
-        <v>0</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>10</v>
+      <c r="F167" s="4">
+        <v>28</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5822,22 +5860,22 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C168" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D168" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="2">
-        <v>0</v>
-      </c>
-      <c r="G168" s="3" t="s">
-        <v>10</v>
+      <c r="F168" s="4">
+        <v>920</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5845,22 +5883,22 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C169" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D169" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="2">
-        <v>0</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>10</v>
+      <c r="F169" s="4">
+        <v>102</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5868,22 +5906,22 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C170" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D170" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="2">
-        <v>0</v>
-      </c>
-      <c r="G170" s="3" t="s">
-        <v>10</v>
+      <c r="F170" s="4">
+        <v>211</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5891,19 +5929,19 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C171" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D171" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E171">
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>0</v>
+        <v>753</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -5914,22 +5952,22 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C172" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D172" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="2">
-        <v>0</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>10</v>
+      <c r="F172" s="4">
+        <v>31</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5937,22 +5975,22 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C173" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D173" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="2">
-        <v>0</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>10</v>
+      <c r="F173" s="4">
+        <v>93</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -5960,22 +5998,22 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C174" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D174" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="2">
-        <v>0</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>10</v>
+      <c r="F174" s="4">
+        <v>378</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -5983,22 +6021,22 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C175" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D175" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="2">
-        <v>0</v>
-      </c>
-      <c r="G175" s="3" t="s">
-        <v>10</v>
+      <c r="F175" s="4">
+        <v>94</v>
+      </c>
+      <c r="G175" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6006,22 +6044,22 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C176" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D176" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="2">
-        <v>0</v>
-      </c>
-      <c r="G176" s="3" t="s">
-        <v>10</v>
+      <c r="F176" s="4">
+        <v>103</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6029,22 +6067,22 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C177" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D177" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="2">
-        <v>0</v>
-      </c>
-      <c r="G177" s="3" t="s">
-        <v>10</v>
+      <c r="F177" s="4">
+        <v>93</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6052,19 +6090,19 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C178" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D178" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E178">
         <v>12</v>
       </c>
       <c r="F178" s="2">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -6075,19 +6113,19 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C179" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D179" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E179">
         <v>12</v>
       </c>
       <c r="F179" s="2">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>10</v>
@@ -6098,22 +6136,22 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C180" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D180" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="6">
         <v>0</v>
       </c>
-      <c r="G180" s="3" t="s">
-        <v>10</v>
+      <c r="G180" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6121,22 +6159,22 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C181" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D181" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="2">
-        <v>0</v>
-      </c>
-      <c r="G181" s="3" t="s">
-        <v>10</v>
+      <c r="F181" s="4">
+        <v>4</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6144,22 +6182,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C182" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D182" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="2">
-        <v>0</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>10</v>
+      <c r="F182" s="4">
+        <v>6</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6167,19 +6205,19 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C183" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D183" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E183">
         <v>1</v>
       </c>
       <c r="F183" s="2">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>10</v>
@@ -6190,19 +6228,19 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C184" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D184" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E184">
         <v>20</v>
       </c>
       <c r="F184" s="2">
-        <v>0</v>
+        <v>3763</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>10</v>
@@ -6213,19 +6251,19 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C185" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D185" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E185">
         <v>20</v>
       </c>
       <c r="F185" s="2">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
@@ -6236,22 +6274,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C186" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D186" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="2">
-        <v>0</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>10</v>
+      <c r="F186" s="4">
+        <v>40</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6259,22 +6297,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C187" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D187" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="2">
-        <v>0</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="F187" s="4">
+        <v>20</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6282,22 +6320,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C188" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D188" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="2">
-        <v>0</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>10</v>
+      <c r="F188" s="4">
+        <v>17</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6305,19 +6343,19 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C189" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D189" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E189">
         <v>50</v>
       </c>
       <c r="F189" s="2">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>10</v>
@@ -6328,19 +6366,19 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C190" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D190" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E190">
         <v>50</v>
       </c>
       <c r="F190" s="2">
-        <v>0</v>
+        <v>1181</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -6351,19 +6389,19 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C191" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D191" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E191">
         <v>50</v>
       </c>
       <c r="F191" s="2">
-        <v>0</v>
+        <v>1873</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6374,19 +6412,19 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C192" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D192" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E192">
         <v>50</v>
       </c>
       <c r="F192" s="2">
-        <v>0</v>
+        <v>1210</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6397,19 +6435,19 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C193" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D193" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E193">
         <v>50</v>
       </c>
       <c r="F193" s="2">
-        <v>0</v>
+        <v>19771</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6420,19 +6458,19 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C194" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D194" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E194">
         <v>100</v>
       </c>
       <c r="F194" s="2">
-        <v>0</v>
+        <v>1181</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
@@ -6443,19 +6481,19 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C195" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D195" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E195">
         <v>60</v>
       </c>
       <c r="F195" s="2">
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6466,19 +6504,19 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C196" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D196" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E196">
         <v>100</v>
       </c>
       <c r="F196" s="2">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>
@@ -6489,19 +6527,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C197" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D197" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E197">
         <v>80</v>
       </c>
       <c r="F197" s="2">
-        <v>0</v>
+        <v>1247</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>6770</v>
+        <v>6590</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>27406</v>
+        <v>27106</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20889</v>
+        <v>20689</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>2766</v>
+        <v>2716</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>2716</v>
+        <v>2596</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>6590</v>
+        <v>6410</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20689</v>
+        <v>20489</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2905,7 +2905,7 @@
         <v>240</v>
       </c>
       <c r="F39" s="4">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>29</v>
@@ -3111,11 +3111,11 @@
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="4">
-        <v>140</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>29</v>
+      <c r="F48" s="6">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3250,7 +3250,7 @@
         <v>720</v>
       </c>
       <c r="F54" s="4">
-        <v>2462</v>
+        <v>2342</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>29</v>
@@ -3319,7 +3319,7 @@
         <v>720</v>
       </c>
       <c r="F57" s="2">
-        <v>4873</v>
+        <v>4633</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>7884</v>
+        <v>7644</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3779,7 +3779,7 @@
         <v>600</v>
       </c>
       <c r="F77" s="4">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>29</v>
@@ -4147,7 +4147,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4170,7 +4170,7 @@
         <v>6</v>
       </c>
       <c r="F94" s="2">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/frontend/public/reports/StockPulse_REPRESENTADAS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="515">
   <si>
     <t>#</t>
   </si>
@@ -43,7 +43,7 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
-    <t>✓ OK</t>
+    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>85007</t>
@@ -100,9 +100,6 @@
     <t>CUCHILLA ARTE AK-4</t>
   </si>
   <si>
-    <t>⚠ BAJO</t>
-  </si>
-  <si>
     <t>85770</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
   </si>
   <si>
     <t>CUCHILLLA DE ARTE AK-5/5B</t>
-  </si>
-  <si>
-    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>85166</t>
@@ -1568,7 +1562,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1587,21 +1581,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF065F46"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFD97706"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1611,16 +1595,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF13DAEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1641,7 +1615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1650,18 +1624,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2054,7 +2016,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>5780</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2039,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>27106</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2100,7 +2062,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="2">
-        <v>7881</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2085,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20189</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2146,7 +2108,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>36463</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -2169,7 +2131,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="2">
-        <v>1027</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -2191,11 +2153,11 @@
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="4">
-        <v>268</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>29</v>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2203,22 +2165,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="4">
-        <v>253</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>29</v>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2226,22 +2188,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="4">
-        <v>59</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>29</v>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2249,22 +2211,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>38</v>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2272,22 +2234,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
         <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
       </c>
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="4">
-        <v>132</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>29</v>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2295,22 +2257,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
         <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
       </c>
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="4">
-        <v>191</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>29</v>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2318,22 +2280,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
         <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
       </c>
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="4">
-        <v>189</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>29</v>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2341,22 +2303,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
         <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
       </c>
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="4">
-        <v>84</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>29</v>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2364,19 +2326,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
         <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
       </c>
       <c r="E16">
         <v>120</v>
       </c>
       <c r="F16" s="2">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -2387,22 +2349,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
         <v>54</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>56</v>
       </c>
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="4">
-        <v>257</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>29</v>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2410,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
         <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" t="s">
-        <v>59</v>
       </c>
       <c r="E18">
         <v>120</v>
       </c>
       <c r="F18" s="2">
-        <v>983</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -2433,22 +2395,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
         <v>60</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
       </c>
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="4">
-        <v>195</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>29</v>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2456,22 +2418,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
         <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>65</v>
       </c>
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="4">
-        <v>75</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>29</v>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2479,22 +2441,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
         <v>66</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
       </c>
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="4">
-        <v>439</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>29</v>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2502,19 +2464,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
         <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
       </c>
       <c r="E22">
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>1803</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2525,22 +2487,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
         <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
       </c>
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="4">
-        <v>3</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>29</v>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2548,22 +2510,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
         <v>75</v>
-      </c>
-      <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" t="s">
-        <v>77</v>
       </c>
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="4">
-        <v>113</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>29</v>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2571,22 +2533,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
         <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>80</v>
       </c>
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="4">
-        <v>348</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>29</v>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2594,22 +2556,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
         <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" t="s">
-        <v>83</v>
       </c>
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="4">
-        <v>123</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>29</v>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2617,22 +2579,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" t="s">
         <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>86</v>
       </c>
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="4">
-        <v>160</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>29</v>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2640,19 +2602,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" t="s">
         <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>89</v>
       </c>
       <c r="E28">
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>8444</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2663,22 +2625,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" t="s">
         <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
       </c>
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="4">
-        <v>94</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>29</v>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2686,22 +2648,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="s">
         <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>95</v>
       </c>
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="4">
-        <v>56</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>29</v>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2709,19 +2671,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" t="s">
         <v>96</v>
-      </c>
-      <c r="C31" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" t="s">
-        <v>98</v>
       </c>
       <c r="E31">
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>2820</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -2732,19 +2694,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" t="s">
         <v>99</v>
-      </c>
-      <c r="C32" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" t="s">
-        <v>101</v>
       </c>
       <c r="E32">
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>1445</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2755,22 +2717,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" t="s">
         <v>102</v>
-      </c>
-      <c r="C33" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
       </c>
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>38</v>
+      <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2778,19 +2740,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" t="s">
         <v>105</v>
-      </c>
-      <c r="C34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
       </c>
       <c r="E34">
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -2801,22 +2763,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" t="s">
         <v>108</v>
-      </c>
-      <c r="C35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" t="s">
-        <v>110</v>
       </c>
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="6">
-        <v>0</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>38</v>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2824,22 +2786,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" t="s">
         <v>111</v>
-      </c>
-      <c r="C36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" t="s">
-        <v>113</v>
       </c>
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="4">
-        <v>118</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>29</v>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2847,22 +2809,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" t="s">
         <v>114</v>
-      </c>
-      <c r="C37" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" t="s">
-        <v>116</v>
       </c>
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="4">
-        <v>944</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>29</v>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2870,22 +2832,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" t="s">
         <v>117</v>
-      </c>
-      <c r="C38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" t="s">
-        <v>119</v>
       </c>
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="4">
-        <v>123</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>29</v>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2893,22 +2855,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" t="s">
         <v>120</v>
-      </c>
-      <c r="C39" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" t="s">
-        <v>122</v>
       </c>
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="4">
-        <v>254</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>29</v>
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2916,22 +2878,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" t="s">
         <v>123</v>
-      </c>
-      <c r="C40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
       </c>
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="4">
-        <v>245</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>29</v>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2939,22 +2901,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" t="s">
         <v>126</v>
-      </c>
-      <c r="C41" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" t="s">
-        <v>128</v>
       </c>
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="4">
-        <v>107</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>29</v>
+      <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2962,22 +2924,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="4">
-        <v>273</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>29</v>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2985,19 +2947,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" t="s">
         <v>131</v>
-      </c>
-      <c r="C43" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" t="s">
-        <v>133</v>
       </c>
       <c r="E43">
         <v>240</v>
       </c>
       <c r="F43" s="2">
-        <v>2865</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -3008,22 +2970,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" t="s">
         <v>134</v>
-      </c>
-      <c r="C44" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" t="s">
-        <v>136</v>
       </c>
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="4">
-        <v>1090</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>29</v>
+      <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3031,22 +2993,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" t="s">
         <v>137</v>
-      </c>
-      <c r="C45" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" t="s">
-        <v>139</v>
       </c>
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="4">
-        <v>163</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>29</v>
+      <c r="F45" s="2">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3054,22 +3016,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>139</v>
+      </c>
+      <c r="D46" t="s">
         <v>140</v>
-      </c>
-      <c r="C46" t="s">
-        <v>141</v>
-      </c>
-      <c r="D46" t="s">
-        <v>142</v>
       </c>
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="4">
-        <v>1475</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>29</v>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3077,22 +3039,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" t="s">
+        <v>142</v>
+      </c>
+      <c r="D47" t="s">
         <v>143</v>
-      </c>
-      <c r="C47" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" t="s">
-        <v>145</v>
       </c>
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="4">
-        <v>164</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>29</v>
+      <c r="F47" s="2">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3100,22 +3062,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="6">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>38</v>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3123,22 +3085,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" t="s">
         <v>148</v>
-      </c>
-      <c r="C49" t="s">
-        <v>149</v>
-      </c>
-      <c r="D49" t="s">
-        <v>150</v>
       </c>
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="4">
-        <v>261</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>29</v>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3146,22 +3108,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" t="s">
         <v>151</v>
-      </c>
-      <c r="C50" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50" t="s">
-        <v>153</v>
       </c>
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="4">
-        <v>291</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>29</v>
+      <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3169,22 +3131,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" t="s">
         <v>154</v>
       </c>
-      <c r="C51" t="s">
-        <v>155</v>
-      </c>
-      <c r="D51" t="s">
-        <v>156</v>
-      </c>
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="4">
-        <v>10</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>29</v>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3192,22 +3154,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" t="s">
+        <v>156</v>
+      </c>
+      <c r="D52" t="s">
         <v>157</v>
-      </c>
-      <c r="C52" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" t="s">
-        <v>159</v>
       </c>
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="4">
-        <v>82</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>29</v>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3215,22 +3177,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" t="s">
         <v>160</v>
-      </c>
-      <c r="C53" t="s">
-        <v>161</v>
-      </c>
-      <c r="D53" t="s">
-        <v>162</v>
       </c>
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="4">
-        <v>27</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>29</v>
+      <c r="F53" s="2">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3238,22 +3200,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" t="s">
         <v>163</v>
-      </c>
-      <c r="C54" t="s">
-        <v>164</v>
-      </c>
-      <c r="D54" t="s">
-        <v>165</v>
       </c>
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="4">
-        <v>2342</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>29</v>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3261,22 +3223,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" t="s">
         <v>166</v>
-      </c>
-      <c r="C55" t="s">
-        <v>167</v>
-      </c>
-      <c r="D55" t="s">
-        <v>168</v>
       </c>
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="4">
-        <v>178</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>29</v>
+      <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3284,22 +3246,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" t="s">
         <v>169</v>
-      </c>
-      <c r="C56" t="s">
-        <v>170</v>
-      </c>
-      <c r="D56" t="s">
-        <v>171</v>
       </c>
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="6">
-        <v>0</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>38</v>
+      <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3307,19 +3269,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" t="s">
         <v>172</v>
-      </c>
-      <c r="C57" t="s">
-        <v>173</v>
-      </c>
-      <c r="D57" t="s">
-        <v>174</v>
       </c>
       <c r="E57">
         <v>720</v>
       </c>
       <c r="F57" s="2">
-        <v>4633</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3330,22 +3292,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" t="s">
+        <v>174</v>
+      </c>
+      <c r="D58" t="s">
         <v>175</v>
-      </c>
-      <c r="C58" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" t="s">
-        <v>177</v>
       </c>
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="4">
-        <v>201</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>29</v>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3353,22 +3315,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" t="s">
+        <v>177</v>
+      </c>
+      <c r="D59" t="s">
         <v>178</v>
-      </c>
-      <c r="C59" t="s">
-        <v>179</v>
-      </c>
-      <c r="D59" t="s">
-        <v>180</v>
       </c>
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="6">
-        <v>0</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>38</v>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3376,22 +3338,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D60" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="6">
-        <v>0</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>38</v>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3399,22 +3361,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" t="s">
         <v>183</v>
-      </c>
-      <c r="C61" t="s">
-        <v>184</v>
-      </c>
-      <c r="D61" t="s">
-        <v>185</v>
       </c>
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="4">
-        <v>300</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>29</v>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3422,22 +3384,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D62" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="4">
-        <v>198</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>29</v>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3445,19 +3407,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" t="s">
         <v>188</v>
-      </c>
-      <c r="C63" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" t="s">
-        <v>190</v>
       </c>
       <c r="E63">
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>7644</v>
+        <v>0</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3468,19 +3430,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" t="s">
         <v>191</v>
-      </c>
-      <c r="C64" t="s">
-        <v>192</v>
-      </c>
-      <c r="D64" t="s">
-        <v>193</v>
       </c>
       <c r="E64">
         <v>60</v>
       </c>
       <c r="F64" s="2">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -3491,22 +3453,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" t="s">
         <v>194</v>
-      </c>
-      <c r="C65" t="s">
-        <v>195</v>
-      </c>
-      <c r="D65" t="s">
-        <v>196</v>
       </c>
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="4">
-        <v>65</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>29</v>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3514,22 +3476,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>195</v>
+      </c>
+      <c r="C66" t="s">
+        <v>196</v>
+      </c>
+      <c r="D66" t="s">
         <v>197</v>
-      </c>
-      <c r="C66" t="s">
-        <v>198</v>
-      </c>
-      <c r="D66" t="s">
-        <v>199</v>
       </c>
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="4">
-        <v>69</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>29</v>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3537,22 +3499,22 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" t="s">
+        <v>199</v>
+      </c>
+      <c r="D67" t="s">
         <v>200</v>
-      </c>
-      <c r="C67" t="s">
-        <v>201</v>
-      </c>
-      <c r="D67" t="s">
-        <v>202</v>
       </c>
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="6">
-        <v>0</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>38</v>
+      <c r="F67" s="2">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3560,22 +3522,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>201</v>
+      </c>
+      <c r="C68" t="s">
+        <v>202</v>
+      </c>
+      <c r="D68" t="s">
         <v>203</v>
-      </c>
-      <c r="C68" t="s">
-        <v>204</v>
-      </c>
-      <c r="D68" t="s">
-        <v>205</v>
       </c>
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="4">
-        <v>55</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>29</v>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3583,19 +3545,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" t="s">
+        <v>205</v>
+      </c>
+      <c r="D69" t="s">
         <v>206</v>
-      </c>
-      <c r="C69" t="s">
-        <v>207</v>
-      </c>
-      <c r="D69" t="s">
-        <v>208</v>
       </c>
       <c r="E69">
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>4170</v>
+        <v>0</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3606,22 +3568,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>207</v>
+      </c>
+      <c r="C70" t="s">
+        <v>208</v>
+      </c>
+      <c r="D70" t="s">
         <v>209</v>
-      </c>
-      <c r="C70" t="s">
-        <v>210</v>
-      </c>
-      <c r="D70" t="s">
-        <v>211</v>
       </c>
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="4">
-        <v>130</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>29</v>
+      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3629,22 +3591,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>210</v>
+      </c>
+      <c r="C71" t="s">
+        <v>211</v>
+      </c>
+      <c r="D71" t="s">
         <v>212</v>
-      </c>
-      <c r="C71" t="s">
-        <v>213</v>
-      </c>
-      <c r="D71" t="s">
-        <v>214</v>
       </c>
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="6">
-        <v>0</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>38</v>
+      <c r="F71" s="2">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3652,22 +3614,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>213</v>
+      </c>
+      <c r="C72" t="s">
+        <v>214</v>
+      </c>
+      <c r="D72" t="s">
         <v>215</v>
-      </c>
-      <c r="C72" t="s">
-        <v>216</v>
-      </c>
-      <c r="D72" t="s">
-        <v>217</v>
       </c>
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="4">
-        <v>412</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>29</v>
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3675,22 +3637,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>216</v>
+      </c>
+      <c r="C73" t="s">
+        <v>217</v>
+      </c>
+      <c r="D73" t="s">
         <v>218</v>
-      </c>
-      <c r="C73" t="s">
-        <v>219</v>
-      </c>
-      <c r="D73" t="s">
-        <v>220</v>
       </c>
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="4">
-        <v>500</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>29</v>
+      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3698,19 +3660,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>219</v>
+      </c>
+      <c r="C74" t="s">
+        <v>220</v>
+      </c>
+      <c r="D74" t="s">
         <v>221</v>
-      </c>
-      <c r="C74" t="s">
-        <v>222</v>
-      </c>
-      <c r="D74" t="s">
-        <v>223</v>
       </c>
       <c r="E74">
         <v>240</v>
       </c>
       <c r="F74" s="2">
-        <v>1356</v>
+        <v>0</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3721,19 +3683,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>222</v>
+      </c>
+      <c r="C75" t="s">
+        <v>223</v>
+      </c>
+      <c r="D75" t="s">
         <v>224</v>
-      </c>
-      <c r="C75" t="s">
-        <v>225</v>
-      </c>
-      <c r="D75" t="s">
-        <v>226</v>
       </c>
       <c r="E75">
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>4001</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3744,22 +3706,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76" t="s">
+        <v>226</v>
+      </c>
+      <c r="D76" t="s">
         <v>227</v>
-      </c>
-      <c r="C76" t="s">
-        <v>228</v>
-      </c>
-      <c r="D76" t="s">
-        <v>229</v>
       </c>
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="6">
-        <v>0</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>38</v>
+      <c r="F76" s="2">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3767,22 +3729,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D77" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="4">
-        <v>529</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>29</v>
+      <c r="F77" s="2">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3790,22 +3752,22 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C78" t="s">
+        <v>231</v>
+      </c>
+      <c r="D78" t="s">
         <v>232</v>
-      </c>
-      <c r="C78" t="s">
-        <v>233</v>
-      </c>
-      <c r="D78" t="s">
-        <v>234</v>
       </c>
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="4">
-        <v>114</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>29</v>
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3813,22 +3775,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>233</v>
+      </c>
+      <c r="C79" t="s">
+        <v>234</v>
+      </c>
+      <c r="D79" t="s">
         <v>235</v>
-      </c>
-      <c r="C79" t="s">
-        <v>236</v>
-      </c>
-      <c r="D79" t="s">
-        <v>237</v>
       </c>
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="4">
-        <v>4</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>29</v>
+      <c r="F79" s="2">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3836,22 +3798,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>236</v>
+      </c>
+      <c r="C80" t="s">
+        <v>237</v>
+      </c>
+      <c r="D80" t="s">
         <v>238</v>
-      </c>
-      <c r="C80" t="s">
-        <v>239</v>
-      </c>
-      <c r="D80" t="s">
-        <v>240</v>
       </c>
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="4">
-        <v>12</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>29</v>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3859,19 +3821,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>239</v>
+      </c>
+      <c r="C81" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" t="s">
         <v>241</v>
-      </c>
-      <c r="C81" t="s">
-        <v>242</v>
-      </c>
-      <c r="D81" t="s">
-        <v>243</v>
       </c>
       <c r="E81">
         <v>20</v>
       </c>
       <c r="F81" s="2">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -3882,19 +3844,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" t="s">
+        <v>243</v>
+      </c>
+      <c r="D82" t="s">
         <v>244</v>
-      </c>
-      <c r="C82" t="s">
-        <v>245</v>
-      </c>
-      <c r="D82" t="s">
-        <v>246</v>
       </c>
       <c r="E82">
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>1896</v>
+        <v>0</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -3905,22 +3867,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>245</v>
+      </c>
+      <c r="C83" t="s">
+        <v>246</v>
+      </c>
+      <c r="D83" t="s">
         <v>247</v>
-      </c>
-      <c r="C83" t="s">
-        <v>248</v>
-      </c>
-      <c r="D83" t="s">
-        <v>249</v>
       </c>
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="6">
-        <v>0</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>38</v>
+      <c r="F83" s="2">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3928,22 +3890,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84" t="s">
+        <v>249</v>
+      </c>
+      <c r="D84" t="s">
         <v>250</v>
-      </c>
-      <c r="C84" t="s">
-        <v>251</v>
-      </c>
-      <c r="D84" t="s">
-        <v>252</v>
       </c>
       <c r="E84">
         <v>40</v>
       </c>
-      <c r="F84" s="4">
-        <v>80</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>29</v>
+      <c r="F84" s="2">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3951,22 +3913,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>251</v>
+      </c>
+      <c r="C85" t="s">
+        <v>252</v>
+      </c>
+      <c r="D85" t="s">
         <v>253</v>
-      </c>
-      <c r="C85" t="s">
-        <v>254</v>
-      </c>
-      <c r="D85" t="s">
-        <v>255</v>
       </c>
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="6">
-        <v>0</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>38</v>
+      <c r="F85" s="2">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3974,22 +3936,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>254</v>
+      </c>
+      <c r="C86" t="s">
+        <v>255</v>
+      </c>
+      <c r="D86" t="s">
         <v>256</v>
-      </c>
-      <c r="C86" t="s">
-        <v>257</v>
-      </c>
-      <c r="D86" t="s">
-        <v>258</v>
       </c>
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="6">
-        <v>0</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>38</v>
+      <c r="F86" s="2">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -3997,22 +3959,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>257</v>
+      </c>
+      <c r="C87" t="s">
+        <v>258</v>
+      </c>
+      <c r="D87" t="s">
         <v>259</v>
-      </c>
-      <c r="C87" t="s">
-        <v>260</v>
-      </c>
-      <c r="D87" t="s">
-        <v>261</v>
       </c>
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="6">
-        <v>0</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>38</v>
+      <c r="F87" s="2">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4020,22 +3982,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>260</v>
+      </c>
+      <c r="C88" t="s">
+        <v>261</v>
+      </c>
+      <c r="D88" t="s">
         <v>262</v>
-      </c>
-      <c r="C88" t="s">
-        <v>263</v>
-      </c>
-      <c r="D88" t="s">
-        <v>264</v>
       </c>
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="4">
-        <v>10</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>29</v>
+      <c r="F88" s="2">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4043,19 +4005,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" t="s">
+        <v>264</v>
+      </c>
+      <c r="D89" t="s">
         <v>265</v>
-      </c>
-      <c r="C89" t="s">
-        <v>266</v>
-      </c>
-      <c r="D89" t="s">
-        <v>267</v>
       </c>
       <c r="E89">
         <v>20</v>
       </c>
       <c r="F89" s="2">
-        <v>1473</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -4066,19 +4028,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>266</v>
+      </c>
+      <c r="C90" t="s">
+        <v>267</v>
+      </c>
+      <c r="D90" t="s">
         <v>268</v>
-      </c>
-      <c r="C90" t="s">
-        <v>269</v>
-      </c>
-      <c r="D90" t="s">
-        <v>270</v>
       </c>
       <c r="E90">
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>108017</v>
+        <v>0</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4089,19 +4051,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>269</v>
+      </c>
+      <c r="C91" t="s">
+        <v>270</v>
+      </c>
+      <c r="D91" t="s">
         <v>271</v>
       </c>
-      <c r="C91" t="s">
-        <v>272</v>
-      </c>
-      <c r="D91" t="s">
-        <v>273</v>
-      </c>
       <c r="E91">
         <v>10</v>
       </c>
       <c r="F91" s="2">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4112,19 +4074,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>272</v>
+      </c>
+      <c r="C92" t="s">
+        <v>273</v>
+      </c>
+      <c r="D92" t="s">
         <v>274</v>
       </c>
-      <c r="C92" t="s">
-        <v>275</v>
-      </c>
-      <c r="D92" t="s">
-        <v>276</v>
-      </c>
       <c r="E92">
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4135,19 +4097,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" t="s">
+        <v>276</v>
+      </c>
+      <c r="D93" t="s">
         <v>277</v>
-      </c>
-      <c r="C93" t="s">
-        <v>278</v>
-      </c>
-      <c r="D93" t="s">
-        <v>279</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4158,19 +4120,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C94" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D94" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E94">
         <v>6</v>
       </c>
       <c r="F94" s="2">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4181,22 +4143,22 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>280</v>
+      </c>
+      <c r="C95" t="s">
+        <v>281</v>
+      </c>
+      <c r="D95" t="s">
         <v>282</v>
-      </c>
-      <c r="C95" t="s">
-        <v>283</v>
-      </c>
-      <c r="D95" t="s">
-        <v>284</v>
       </c>
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="6">
-        <v>0</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>38</v>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4204,22 +4166,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D96" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="6">
-        <v>0</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>38</v>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4227,22 +4189,22 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>285</v>
+      </c>
+      <c r="C97" t="s">
+        <v>286</v>
+      </c>
+      <c r="D97" t="s">
         <v>287</v>
       </c>
-      <c r="C97" t="s">
-        <v>288</v>
-      </c>
-      <c r="D97" t="s">
-        <v>289</v>
-      </c>
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="4">
-        <v>7</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>29</v>
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4250,22 +4212,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>288</v>
+      </c>
+      <c r="C98" t="s">
+        <v>289</v>
+      </c>
+      <c r="D98" t="s">
         <v>290</v>
-      </c>
-      <c r="C98" t="s">
-        <v>291</v>
-      </c>
-      <c r="D98" t="s">
-        <v>292</v>
       </c>
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="6">
-        <v>0</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>38</v>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4273,22 +4235,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>291</v>
+      </c>
+      <c r="C99" t="s">
+        <v>292</v>
+      </c>
+      <c r="D99" t="s">
         <v>293</v>
-      </c>
-      <c r="C99" t="s">
-        <v>294</v>
-      </c>
-      <c r="D99" t="s">
-        <v>295</v>
       </c>
       <c r="E99">
         <v>5</v>
       </c>
-      <c r="F99" s="6">
-        <v>0</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>38</v>
+      <c r="F99" s="2">
+        <v>0</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4296,19 +4258,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>294</v>
+      </c>
+      <c r="C100" t="s">
+        <v>295</v>
+      </c>
+      <c r="D100" t="s">
         <v>296</v>
-      </c>
-      <c r="C100" t="s">
-        <v>297</v>
-      </c>
-      <c r="D100" t="s">
-        <v>298</v>
       </c>
       <c r="E100">
         <v>6</v>
       </c>
       <c r="F100" s="2">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4319,19 +4281,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>297</v>
+      </c>
+      <c r="C101" t="s">
+        <v>298</v>
+      </c>
+      <c r="D101" t="s">
         <v>299</v>
-      </c>
-      <c r="C101" t="s">
-        <v>300</v>
-      </c>
-      <c r="D101" t="s">
-        <v>301</v>
       </c>
       <c r="E101">
         <v>6</v>
       </c>
       <c r="F101" s="2">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4342,19 +4304,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>300</v>
+      </c>
+      <c r="C102" t="s">
+        <v>301</v>
+      </c>
+      <c r="D102" t="s">
         <v>302</v>
-      </c>
-      <c r="C102" t="s">
-        <v>303</v>
-      </c>
-      <c r="D102" t="s">
-        <v>304</v>
       </c>
       <c r="E102">
         <v>6</v>
       </c>
       <c r="F102" s="2">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4365,19 +4327,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>303</v>
+      </c>
+      <c r="C103" t="s">
+        <v>304</v>
+      </c>
+      <c r="D103" t="s">
         <v>305</v>
-      </c>
-      <c r="C103" t="s">
-        <v>306</v>
-      </c>
-      <c r="D103" t="s">
-        <v>307</v>
       </c>
       <c r="E103">
         <v>6</v>
       </c>
       <c r="F103" s="2">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>10</v>
@@ -4388,22 +4350,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>306</v>
+      </c>
+      <c r="C104" t="s">
+        <v>307</v>
+      </c>
+      <c r="D104" t="s">
         <v>308</v>
-      </c>
-      <c r="C104" t="s">
-        <v>309</v>
-      </c>
-      <c r="D104" t="s">
-        <v>310</v>
       </c>
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="4">
-        <v>4</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>29</v>
+      <c r="F104" s="2">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4411,19 +4373,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>309</v>
+      </c>
+      <c r="C105" t="s">
+        <v>310</v>
+      </c>
+      <c r="D105" t="s">
         <v>311</v>
-      </c>
-      <c r="C105" t="s">
-        <v>312</v>
-      </c>
-      <c r="D105" t="s">
-        <v>313</v>
       </c>
       <c r="E105">
         <v>56</v>
       </c>
       <c r="F105" s="2">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>10</v>
@@ -4434,22 +4396,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>312</v>
+      </c>
+      <c r="C106" t="s">
+        <v>313</v>
+      </c>
+      <c r="D106" t="s">
         <v>314</v>
-      </c>
-      <c r="C106" t="s">
-        <v>315</v>
-      </c>
-      <c r="D106" t="s">
-        <v>316</v>
       </c>
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="4">
-        <v>15</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>29</v>
+      <c r="F106" s="2">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4457,22 +4419,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>315</v>
+      </c>
+      <c r="C107" t="s">
+        <v>316</v>
+      </c>
+      <c r="D107" t="s">
         <v>317</v>
-      </c>
-      <c r="C107" t="s">
-        <v>318</v>
-      </c>
-      <c r="D107" t="s">
-        <v>319</v>
       </c>
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="4">
-        <v>1</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>29</v>
+      <c r="F107" s="2">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4480,22 +4442,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>318</v>
+      </c>
+      <c r="C108" t="s">
+        <v>319</v>
+      </c>
+      <c r="D108" t="s">
         <v>320</v>
-      </c>
-      <c r="C108" t="s">
-        <v>321</v>
-      </c>
-      <c r="D108" t="s">
-        <v>322</v>
       </c>
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="4">
-        <v>79</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>29</v>
+      <c r="F108" s="2">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4503,22 +4465,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C109" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D109" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="6">
-        <v>0</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>38</v>
+      <c r="F109" s="2">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4526,22 +4488,22 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>323</v>
+      </c>
+      <c r="C110" t="s">
+        <v>324</v>
+      </c>
+      <c r="D110" t="s">
         <v>325</v>
-      </c>
-      <c r="C110" t="s">
-        <v>326</v>
-      </c>
-      <c r="D110" t="s">
-        <v>327</v>
       </c>
       <c r="E110">
         <v>54</v>
       </c>
-      <c r="F110" s="4">
-        <v>93</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>29</v>
+      <c r="F110" s="2">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4549,22 +4511,22 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D111" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="6">
-        <v>0</v>
-      </c>
-      <c r="G111" s="7" t="s">
-        <v>38</v>
+      <c r="F111" s="2">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4572,22 +4534,22 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C112" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D112" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="6">
-        <v>0</v>
-      </c>
-      <c r="G112" s="7" t="s">
-        <v>38</v>
+      <c r="F112" s="2">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4595,22 +4557,22 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C113" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D113" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="6">
-        <v>0</v>
-      </c>
-      <c r="G113" s="7" t="s">
-        <v>38</v>
+      <c r="F113" s="2">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4618,19 +4580,19 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C114" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D114" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E114">
         <v>5</v>
       </c>
       <c r="F114" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4641,22 +4603,22 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C115" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D115" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="4">
-        <v>312</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>29</v>
+      <c r="F115" s="2">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4664,22 +4626,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C116" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D116" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="6">
-        <v>0</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>38</v>
+      <c r="F116" s="2">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4687,22 +4649,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C117" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D117" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="4">
-        <v>2</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>29</v>
+      <c r="F117" s="2">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4710,19 +4672,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C118" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D118" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E118">
         <v>10</v>
       </c>
       <c r="F118" s="2">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -4733,22 +4695,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C119" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D119" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="4">
-        <v>6</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>29</v>
+      <c r="F119" s="2">
+        <v>0</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4756,22 +4718,22 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C120" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D120" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="4">
-        <v>36</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>29</v>
+      <c r="F120" s="2">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4779,22 +4741,22 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C121" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D121" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="6">
-        <v>0</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>38</v>
+      <c r="F121" s="2">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4802,22 +4764,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C122" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D122" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="6">
-        <v>0</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>38</v>
+      <c r="F122" s="2">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4825,22 +4787,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C123" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D123" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="4">
-        <v>127</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>29</v>
+      <c r="F123" s="2">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4848,19 +4810,19 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C124" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D124" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E124">
         <v>4</v>
       </c>
       <c r="F124" s="2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -4871,22 +4833,22 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
+        <v>354</v>
+      </c>
+      <c r="C125" t="s">
+        <v>355</v>
+      </c>
+      <c r="D125" t="s">
         <v>356</v>
-      </c>
-      <c r="C125" t="s">
-        <v>357</v>
-      </c>
-      <c r="D125" t="s">
-        <v>358</v>
       </c>
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="6">
-        <v>0</v>
-      </c>
-      <c r="G125" s="7" t="s">
-        <v>38</v>
+      <c r="F125" s="2">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4894,22 +4856,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C126" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D126" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="4">
-        <v>17</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>29</v>
+      <c r="F126" s="2">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4917,19 +4879,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C127" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D127" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E127">
         <v>4</v>
       </c>
       <c r="F127" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>10</v>
@@ -4940,22 +4902,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C128" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D128" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="4">
-        <v>18</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>29</v>
+      <c r="F128" s="2">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4963,22 +4925,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C129" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D129" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="4">
-        <v>4</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>29</v>
+      <c r="F129" s="2">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4986,22 +4948,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C130" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D130" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="4">
-        <v>3</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>29</v>
+      <c r="F130" s="2">
+        <v>0</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5009,19 +4971,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D131" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E131">
         <v>60</v>
       </c>
       <c r="F131" s="2">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -5032,22 +4994,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C132" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D132" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="4">
-        <v>58</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>29</v>
+      <c r="F132" s="2">
+        <v>0</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5055,22 +5017,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C133" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D133" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="4">
-        <v>138</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>29</v>
+      <c r="F133" s="2">
+        <v>0</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5078,19 +5040,19 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C134" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D134" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E134">
         <v>60</v>
       </c>
       <c r="F134" s="2">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>10</v>
@@ -5101,19 +5063,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C135" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E135">
         <v>60</v>
       </c>
       <c r="F135" s="2">
-        <v>521</v>
+        <v>0</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>10</v>
@@ -5124,19 +5086,19 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C136" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D136" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E136">
         <v>60</v>
       </c>
       <c r="F136" s="2">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>10</v>
@@ -5147,19 +5109,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C137" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E137">
         <v>30</v>
       </c>
       <c r="F137" s="2">
-        <v>1601</v>
+        <v>0</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>10</v>
@@ -5170,19 +5132,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C138" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E138">
         <v>40</v>
       </c>
       <c r="F138" s="2">
-        <v>1130</v>
+        <v>0</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>10</v>
@@ -5193,19 +5155,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C139" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E139">
         <v>63</v>
       </c>
       <c r="F139" s="2">
-        <v>566</v>
+        <v>0</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
@@ -5216,19 +5178,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C140" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E140">
         <v>10</v>
       </c>
       <c r="F140" s="2">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>10</v>
@@ -5239,22 +5201,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C141" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="4">
-        <v>108</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>29</v>
+      <c r="F141" s="2">
+        <v>0</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5262,22 +5224,22 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C142" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="4">
-        <v>122</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>29</v>
+      <c r="F142" s="2">
+        <v>0</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5285,22 +5247,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C143" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D143" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="4">
-        <v>15</v>
-      </c>
-      <c r="G143" s="5" t="s">
-        <v>29</v>
+      <c r="F143" s="2">
+        <v>0</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5308,22 +5270,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C144" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D144" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="6">
-        <v>0</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>38</v>
+      <c r="F144" s="2">
+        <v>0</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5331,22 +5293,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C145" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D145" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="4">
-        <v>10</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>29</v>
+      <c r="F145" s="2">
+        <v>0</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5354,22 +5316,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C146" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D146" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="4">
-        <v>34</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>29</v>
+      <c r="F146" s="2">
+        <v>0</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5377,22 +5339,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C147" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D147" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="6">
-        <v>0</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>38</v>
+      <c r="F147" s="2">
+        <v>0</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5400,19 +5362,19 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C148" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D148" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E148">
         <v>5</v>
       </c>
       <c r="F148" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>10</v>
@@ -5423,19 +5385,19 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C149" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E149">
         <v>5</v>
       </c>
       <c r="F149" s="2">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>10</v>
@@ -5446,19 +5408,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C150" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D150" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E150">
         <v>5</v>
       </c>
       <c r="F150" s="2">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -5469,19 +5431,19 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C151" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D151" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151" s="2">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5492,22 +5454,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C152" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D152" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="4">
-        <v>8</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>29</v>
+      <c r="F152" s="2">
+        <v>0</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5515,22 +5477,22 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C153" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="4">
-        <v>640</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>29</v>
+      <c r="F153" s="2">
+        <v>0</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5538,22 +5500,22 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>413</v>
+      </c>
+      <c r="C154" t="s">
+        <v>414</v>
+      </c>
+      <c r="D154" t="s">
         <v>415</v>
-      </c>
-      <c r="C154" t="s">
-        <v>416</v>
-      </c>
-      <c r="D154" t="s">
-        <v>417</v>
       </c>
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="4">
-        <v>121</v>
-      </c>
-      <c r="G154" s="5" t="s">
-        <v>29</v>
+      <c r="F154" s="2">
+        <v>0</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5561,19 +5523,19 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C155" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E155">
         <v>60</v>
       </c>
       <c r="F155" s="2">
-        <v>855</v>
+        <v>0</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>10</v>
@@ -5584,22 +5546,22 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C156" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D156" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="6">
-        <v>0</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>38</v>
+      <c r="F156" s="2">
+        <v>0</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5607,22 +5569,22 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>420</v>
+      </c>
+      <c r="C157" t="s">
+        <v>421</v>
+      </c>
+      <c r="D157" t="s">
         <v>422</v>
-      </c>
-      <c r="C157" t="s">
-        <v>423</v>
-      </c>
-      <c r="D157" t="s">
-        <v>424</v>
       </c>
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="4">
-        <v>66</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>29</v>
+      <c r="F157" s="2">
+        <v>0</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5630,22 +5592,22 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C158" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="4">
-        <v>30</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>29</v>
+      <c r="F158" s="2">
+        <v>0</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5653,22 +5615,22 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>425</v>
+      </c>
+      <c r="C159" t="s">
+        <v>426</v>
+      </c>
+      <c r="D159" t="s">
         <v>427</v>
-      </c>
-      <c r="C159" t="s">
-        <v>428</v>
-      </c>
-      <c r="D159" t="s">
-        <v>429</v>
       </c>
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="4">
-        <v>83</v>
-      </c>
-      <c r="G159" s="5" t="s">
-        <v>29</v>
+      <c r="F159" s="2">
+        <v>0</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5676,22 +5638,22 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>428</v>
+      </c>
+      <c r="C160" t="s">
+        <v>429</v>
+      </c>
+      <c r="D160" t="s">
         <v>430</v>
-      </c>
-      <c r="C160" t="s">
-        <v>431</v>
-      </c>
-      <c r="D160" t="s">
-        <v>432</v>
       </c>
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="4">
-        <v>10</v>
-      </c>
-      <c r="G160" s="5" t="s">
-        <v>29</v>
+      <c r="F160" s="2">
+        <v>0</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5699,22 +5661,22 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C161" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D161" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="4">
-        <v>51</v>
-      </c>
-      <c r="G161" s="5" t="s">
-        <v>29</v>
+      <c r="F161" s="2">
+        <v>0</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5722,22 +5684,22 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C162" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D162" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="4">
-        <v>74</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>29</v>
+      <c r="F162" s="2">
+        <v>0</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5745,22 +5707,22 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C163" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D163" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="4">
-        <v>11</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>29</v>
+      <c r="F163" s="2">
+        <v>0</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5768,22 +5730,22 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C164" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D164" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="4">
-        <v>4</v>
-      </c>
-      <c r="G164" s="5" t="s">
-        <v>29</v>
+      <c r="F164" s="2">
+        <v>0</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5791,22 +5753,22 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C165" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D165" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="4">
-        <v>35</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>29</v>
+      <c r="F165" s="2">
+        <v>0</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5814,22 +5776,22 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>441</v>
+      </c>
+      <c r="C166" t="s">
+        <v>442</v>
+      </c>
+      <c r="D166" t="s">
         <v>443</v>
-      </c>
-      <c r="C166" t="s">
-        <v>444</v>
-      </c>
-      <c r="D166" t="s">
-        <v>445</v>
       </c>
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="4">
-        <v>62</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>29</v>
+      <c r="F166" s="2">
+        <v>0</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5837,22 +5799,22 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>444</v>
+      </c>
+      <c r="C167" t="s">
+        <v>445</v>
+      </c>
+      <c r="D167" t="s">
         <v>446</v>
-      </c>
-      <c r="C167" t="s">
-        <v>447</v>
-      </c>
-      <c r="D167" t="s">
-        <v>448</v>
       </c>
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="4">
-        <v>28</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>29</v>
+      <c r="F167" s="2">
+        <v>0</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5860,22 +5822,22 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C168" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D168" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="4">
-        <v>920</v>
-      </c>
-      <c r="G168" s="5" t="s">
-        <v>29</v>
+      <c r="F168" s="2">
+        <v>0</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5883,22 +5845,22 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C169" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D169" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="4">
-        <v>102</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>29</v>
+      <c r="F169" s="2">
+        <v>0</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5906,22 +5868,22 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C170" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D170" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="4">
-        <v>211</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>29</v>
+      <c r="F170" s="2">
+        <v>0</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5929,19 +5891,19 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C171" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D171" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E171">
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>753</v>
+        <v>0</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -5952,22 +5914,22 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C172" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D172" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="4">
-        <v>31</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>29</v>
+      <c r="F172" s="2">
+        <v>0</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5975,22 +5937,22 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C173" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D173" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="4">
-        <v>93</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>29</v>
+      <c r="F173" s="2">
+        <v>0</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -5998,22 +5960,22 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C174" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D174" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="4">
-        <v>378</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>29</v>
+      <c r="F174" s="2">
+        <v>0</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6021,22 +5983,22 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C175" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D175" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="4">
-        <v>94</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>29</v>
+      <c r="F175" s="2">
+        <v>0</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6044,22 +6006,22 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
+        <v>463</v>
+      </c>
+      <c r="C176" t="s">
+        <v>464</v>
+      </c>
+      <c r="D176" t="s">
         <v>465</v>
-      </c>
-      <c r="C176" t="s">
-        <v>466</v>
-      </c>
-      <c r="D176" t="s">
-        <v>467</v>
       </c>
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="4">
-        <v>103</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>29</v>
+      <c r="F176" s="2">
+        <v>0</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6067,22 +6029,22 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
+        <v>466</v>
+      </c>
+      <c r="C177" t="s">
+        <v>467</v>
+      </c>
+      <c r="D177" t="s">
         <v>468</v>
-      </c>
-      <c r="C177" t="s">
-        <v>469</v>
-      </c>
-      <c r="D177" t="s">
-        <v>470</v>
       </c>
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="4">
-        <v>93</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>29</v>
+      <c r="F177" s="2">
+        <v>0</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6090,19 +6052,19 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C178" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D178" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E178">
         <v>12</v>
       </c>
       <c r="F178" s="2">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -6113,19 +6075,19 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C179" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D179" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E179">
         <v>12</v>
       </c>
       <c r="F179" s="2">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>10</v>
@@ -6136,22 +6098,22 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C180" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D180" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="6">
-        <v>0</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>38</v>
+      <c r="F180" s="2">
+        <v>0</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6159,22 +6121,22 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C181" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D181" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="4">
-        <v>4</v>
-      </c>
-      <c r="G181" s="5" t="s">
-        <v>29</v>
+      <c r="F181" s="2">
+        <v>0</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6182,22 +6144,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C182" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D182" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="4">
-        <v>6</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>29</v>
+      <c r="F182" s="2">
+        <v>0</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6205,19 +6167,19 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C183" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D183" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E183">
         <v>1</v>
       </c>
       <c r="F183" s="2">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>10</v>
@@ -6228,19 +6190,19 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C184" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D184" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E184">
         <v>20</v>
       </c>
       <c r="F184" s="2">
-        <v>3763</v>
+        <v>0</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>10</v>
@@ -6251,19 +6213,19 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C185" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D185" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E185">
         <v>20</v>
       </c>
       <c r="F185" s="2">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
@@ -6274,22 +6236,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C186" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D186" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="4">
-        <v>40</v>
-      </c>
-      <c r="G186" s="5" t="s">
-        <v>29</v>
+      <c r="F186" s="2">
+        <v>0</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6297,22 +6259,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C187" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D187" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="4">
-        <v>20</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>29</v>
+      <c r="F187" s="2">
+        <v>0</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6320,22 +6282,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C188" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D188" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="4">
-        <v>17</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>29</v>
+      <c r="F188" s="2">
+        <v>0</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6343,19 +6305,19 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C189" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D189" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E189">
         <v>50</v>
       </c>
       <c r="F189" s="2">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>10</v>
@@ -6366,19 +6328,19 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C190" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D190" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E190">
         <v>50</v>
       </c>
       <c r="F190" s="2">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -6389,19 +6351,19 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>495</v>
+      </c>
+      <c r="C191" t="s">
+        <v>496</v>
+      </c>
+      <c r="D191" t="s">
         <v>497</v>
-      </c>
-      <c r="C191" t="s">
-        <v>498</v>
-      </c>
-      <c r="D191" t="s">
-        <v>499</v>
       </c>
       <c r="E191">
         <v>50</v>
       </c>
       <c r="F191" s="2">
-        <v>1373</v>
+        <v>0</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6412,19 +6374,19 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>498</v>
+      </c>
+      <c r="C192" t="s">
+        <v>499</v>
+      </c>
+      <c r="D192" t="s">
         <v>500</v>
-      </c>
-      <c r="C192" t="s">
-        <v>501</v>
-      </c>
-      <c r="D192" t="s">
-        <v>502</v>
       </c>
       <c r="E192">
         <v>50</v>
       </c>
       <c r="F192" s="2">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6435,19 +6397,19 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>501</v>
+      </c>
+      <c r="C193" t="s">
+        <v>502</v>
+      </c>
+      <c r="D193" t="s">
         <v>503</v>
-      </c>
-      <c r="C193" t="s">
-        <v>504</v>
-      </c>
-      <c r="D193" t="s">
-        <v>505</v>
       </c>
       <c r="E193">
         <v>50</v>
       </c>
       <c r="F193" s="2">
-        <v>19771</v>
+        <v>0</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6458,19 +6420,19 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>504</v>
+      </c>
+      <c r="C194" t="s">
+        <v>505</v>
+      </c>
+      <c r="D194" t="s">
         <v>506</v>
-      </c>
-      <c r="C194" t="s">
-        <v>507</v>
-      </c>
-      <c r="D194" t="s">
-        <v>508</v>
       </c>
       <c r="E194">
         <v>100</v>
       </c>
       <c r="F194" s="2">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
@@ -6481,19 +6443,19 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
+        <v>507</v>
+      </c>
+      <c r="C195" t="s">
+        <v>508</v>
+      </c>
+      <c r="D195" t="s">
         <v>509</v>
-      </c>
-      <c r="C195" t="s">
-        <v>510</v>
-      </c>
-      <c r="D195" t="s">
-        <v>511</v>
       </c>
       <c r="E195">
         <v>60</v>
       </c>
       <c r="F195" s="2">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6504,19 +6466,19 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C196" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D196" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E196">
         <v>100</v>
       </c>
       <c r="F196" s="2">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>
@@ -6527,19 +6489,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
+        <v>512</v>
+      </c>
+      <c r="C197" t="s">
+        <v>513</v>
+      </c>
+      <c r="D197" t="s">
         <v>514</v>
-      </c>
-      <c r="C197" t="s">
-        <v>515</v>
-      </c>
-      <c r="D197" t="s">
-        <v>516</v>
       </c>
       <c r="E197">
         <v>80</v>
       </c>
       <c r="F197" s="2">
-        <v>1247</v>
+        <v>0</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>10</v>
